--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -866,13 +866,13 @@
         <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
@@ -1138,203 +1138,203 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>1.14</v>
       </c>
       <c r="T3" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="T4" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1670,7 +1670,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
         <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>1.39</v>
       </c>
       <c r="H9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
         <v>11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
         <v>1.95</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
         <v>3.8</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
         <v>1.76</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3397,28 +3397,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
         <v>1.1</v>
@@ -3427,200 +3427,200 @@
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>1.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.09</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3678,13 +3678,13 @@
         <v>1.26</v>
       </c>
       <c r="O13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P13" t="n">
         <v>1.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4413,230 +4413,230 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="G16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H16" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.26</v>
       </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>2.22</v>
+        <v>1.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="X16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4921,230 +4921,230 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I20" t="n">
         <v>2.18</v>
@@ -5444,7 +5444,7 @@
         <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -5707,13 +5707,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
         <v>1.98</v>
@@ -5722,7 +5722,7 @@
         <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
         <v>1.11</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G22" t="n">
         <v>1.8</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
         <v>6.2</v>
@@ -5952,7 +5952,7 @@
         <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
         <v>2.28</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
         <v>1.02</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,13 +6215,13 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.01</v>
       </c>
       <c r="P23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
         <v>1.31</v>
@@ -6230,7 +6230,7 @@
         <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>2.72</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
         <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,13 +6469,13 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
         <v>1.01</v>
       </c>
       <c r="P24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q24" t="n">
         <v>1.31</v>
@@ -6484,7 +6484,7 @@
         <v>1.16</v>
       </c>
       <c r="S24" t="n">
-        <v>2.72</v>
+        <v>1.31</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Liaoning Tieren FC</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shandong Taishan</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.96</v>
+        <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="H2" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.74</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>Dalian Kun City FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>Shenzhen Juniors FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Laholms</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Utsiktens</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>2.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Stockholm Internazionale</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H5" t="n">
-        <v>1.37</v>
+        <v>2.84</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.38</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.64</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shenzhen Peng City</t>
+          <t>Laholms</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Utsiktens</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP6" t="n">
         <v>4.2</v>
       </c>
-      <c r="G6" t="n">
+      <c r="AQ6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4.7</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="AT6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="AW6" t="n">
         <v>4.5</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Henan Songshan Longmen</t>
+          <t>FC Stockholm Internazionale</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shanghai Port FC</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.22</v>
+        <v>1.36</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.16</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chongqing Tonglianglong</t>
+          <t>Shijiazhuang Gongfu FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger FC</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.91</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Nantong Zhiyun F.C</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J9" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Foshan Nanshi FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.86</v>
+        <v>2.76</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Guangdong GZ-Power FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Shaanxi Union FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>1.77</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>Shanghai Port FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.26</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.09</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Chongqing Tonglianglong</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>Tianjin Jinmen Tiger FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>1.39</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skovde AIK</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.05</v>
+        <v>1.93</v>
       </c>
       <c r="G16" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.09</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.26</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q18" t="n">
         <v>1.01</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>2.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Skovde AIK</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.75</v>
+        <v>1.51</v>
       </c>
       <c r="G20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X20" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV20" t="n">
         <v>4.2</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="AW20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX20" t="n">
         <v>3.65</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK21" t="n">
         <v>4.4</v>
       </c>
-      <c r="G21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,36 +5923,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.73</v>
+        <v>2.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8</v>
+        <v>3.45</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>2.94</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,33 +6177,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deportes Rengo Unido</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colchagua CD</t>
+          <t>IFK Stocksund</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,34 +6215,34 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.25</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6407,268 +6407,1792 @@
         <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FC Arlanda</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IF Karlstad</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>25</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-25 05:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Volsungur</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Grotta</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-25 05:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ostersunds FK</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-25 05:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-25 05:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-25 05:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Chilean Segunda Division</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Deportes Rengo Unido</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Colchagua CD</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-25 05:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chilean Segunda Division</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Concon National FC</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Deportes Colina</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="F30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J30" t="n">
         <v>1.02</v>
       </c>
-      <c r="K24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="K30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
         <v>1.25</v>
       </c>
-      <c r="O24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="O30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q30" t="n">
         <v>1.31</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R30" t="n">
         <v>1.16</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S30" t="n">
         <v>1.31</v>
       </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AQ30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AR30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AS30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AT30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AU30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AV30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AW30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AX30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="AY30" t="n">
         <v>1.03</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="AZ30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BA30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BB30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BC30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BD30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BE30" t="n">
         <v>1.03</v>
       </c>
-      <c r="BF24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB24" t="inlineStr">
-        <is>
-          <t>2026-06-25 02:56:45</t>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H2" t="n">
         <v>2.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="J2" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.58</v>
+        <v>2.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.92</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,43 +905,43 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -950,7 +950,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BH2" t="n">
         <v>4</v>
@@ -1028,59 +1028,59 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J4" t="n">
         <v>3.9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>2.84</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1649,7 +1649,7 @@
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q5" t="n">
         <v>1.46</v>
@@ -1658,7 +1658,7 @@
         <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
         <v>1.47</v>
@@ -1703,7 +1703,7 @@
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
         <v>38</v>
@@ -1727,55 +1727,55 @@
         <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4</v>
-      </c>
       <c r="AY5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ5" t="n">
         <v>3.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
         <v>4.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG5" t="n">
         <v>4.1</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="T6" t="n">
         <v>1.58</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.69</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
         <v>1.16</v>
@@ -2178,7 +2178,7 @@
         <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H9" t="n">
-        <v>1.23</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="K10" t="n">
         <v>3.45</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="H11" t="n">
-        <v>1.77</v>
+        <v>3.55</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
         <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>2.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5432,16 +5432,16 @@
         <v>1.51</v>
       </c>
       <c r="G20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H20" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
         <v>5.8</v>
@@ -5480,7 +5480,7 @@
         <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X20" t="n">
         <v>32</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5716,13 +5716,13 @@
         <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R21" t="n">
         <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="T21" t="n">
         <v>1.58</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>1.95</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,7 +6215,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O23" t="n">
         <v>1.1</v>
@@ -6239,10 +6239,10 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6702,16 +6702,16 @@
         <v>2.94</v>
       </c>
       <c r="G25" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H25" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I25" t="n">
         <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
@@ -6729,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
         <v>1.38</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
         <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
         <v>1.41</v>
@@ -7237,7 +7237,7 @@
         <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>1.73</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H28" t="n">
         <v>6</v>
@@ -7473,10 +7473,10 @@
         <v>6.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
         <v>1.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P29" t="n">
         <v>1.25</v>
@@ -7754,7 +7754,7 @@
         <v>1.16</v>
       </c>
       <c r="S29" t="n">
-        <v>1.31</v>
+        <v>2.36</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7993,13 +7993,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O30" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
         <v>1.31</v>
@@ -8008,7 +8008,7 @@
         <v>1.16</v>
       </c>
       <c r="S30" t="n">
-        <v>1.31</v>
+        <v>2.36</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G2" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -896,25 +896,25 @@
         <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
         <v>21</v>
@@ -929,10 +929,10 @@
         <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AF2" t="n">
         <v>24</v>
@@ -941,7 +941,7 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>50</v>
@@ -956,7 +956,7 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
         <v>40</v>
@@ -965,28 +965,28 @@
         <v>30</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
         <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
@@ -998,43 +998,43 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.48</v>
+        <v>1.53</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.63</v>
+        <v>1.16</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.69</v>
+        <v>1.19</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -1123,25 +1123,25 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.02</v>
       </c>
-      <c r="K3" t="n">
-        <v>950</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
         <v>1.52</v>
@@ -1150,19 +1150,19 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,16 +1389,16 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1646,7 +1646,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.25</v>
@@ -1658,19 +1658,19 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
         <v>4.2</v>
@@ -1891,19 +1891,19 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
         <v>1.83</v>
@@ -1912,13 +1912,13 @@
         <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V6" t="n">
         <v>1.31</v>
@@ -1939,7 +1939,7 @@
         <v>80</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
         <v>9.199999999999999</v>
@@ -1954,7 +1954,7 @@
         <v>16.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>20</v>
@@ -1981,58 +1981,58 @@
         <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU6" t="n">
         <v>5.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BG6" t="n">
         <v>5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH6" t="n">
         <v>3.75</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="I7" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="J7" t="n">
         <v>3.9</v>
@@ -2157,7 +2157,7 @@
         <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q7" t="n">
         <v>1.47</v>
@@ -2175,10 +2175,10 @@
         <v>2.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>36</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG7" t="n">
         <v>17.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="n">
         <v>32</v>
@@ -2220,31 +2220,31 @@
         <v>60</v>
       </c>
       <c r="AK7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL7" t="n">
         <v>36</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>38</v>
       </c>
       <c r="AM7" t="n">
         <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO7" t="n">
         <v>12</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AQ7" t="n">
         <v>15</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
         <v>17.5</v>
@@ -2256,40 +2256,40 @@
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>19.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
         <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BE7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI7" t="n">
         <v>3.75</v>
@@ -2298,59 +2298,59 @@
         <v>8.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
         <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP7" t="n">
         <v>21</v>
       </c>
       <c r="BQ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS7" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>7.2</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX7" t="n">
         <v>22</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>14</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -2668,19 +2668,19 @@
         <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
         <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
         <v>1.47</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V9" t="n">
         <v>1.37</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>1.9</v>
       </c>
       <c r="H10" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
         <v>5.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -3409,22 +3409,22 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.02</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.25</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3678,7 +3678,7 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
         <v>1.25</v>
@@ -3699,10 +3699,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G14" t="n">
         <v>2.18</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
         <v>4.6</v>
@@ -4067,7 +4067,7 @@
         <v>5.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BI14" t="n">
         <v>2.56</v>
@@ -4076,59 +4076,59 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -4171,10 +4171,10 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4186,31 +4186,31 @@
         <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P15" t="n">
         <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         <v>5.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
@@ -4452,7 +4452,7 @@
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
         <v>2.06</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G17" t="n">
         <v>3.4</v>
@@ -4676,7 +4676,7 @@
         <v>2.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
@@ -4691,10 +4691,10 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
         <v>1.53</v>
@@ -4709,16 +4709,16 @@
         <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4832,7 +4832,7 @@
         <v>3.25</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -4924,22 +4924,22 @@
         <v>2.78</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
         <v>2.68</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J18" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
@@ -4960,7 +4960,7 @@
         <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.84</v>
@@ -4969,7 +4969,7 @@
         <v>1.87</v>
       </c>
       <c r="V18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
         <v>1.43</v>
@@ -5014,7 +5014,7 @@
         <v>60</v>
       </c>
       <c r="AK18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
         <v>70</v>
@@ -5059,7 +5059,7 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -5217,10 +5217,10 @@
         <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V19" t="n">
         <v>2.08</v>
@@ -5376,7 +5376,7 @@
         <v>5</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV19" t="n">
         <v>12.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>2.32</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I20" t="n">
         <v>3.65</v>
@@ -5477,7 +5477,7 @@
         <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
         <v>1.75</v>
@@ -5594,7 +5594,7 @@
         <v>3.7</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
         <v>1.39</v>
       </c>
       <c r="R22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S22" t="n">
         <v>1.98</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1.97</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,7 +6215,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.28</v>
@@ -6224,19 +6224,19 @@
         <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>2.02</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>2.94</v>
       </c>
       <c r="H24" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I24" t="n">
         <v>3.6</v>
@@ -6472,13 +6472,13 @@
         <v>2.38</v>
       </c>
       <c r="O24" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
         <v>1.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R24" t="n">
         <v>1.14</v>
@@ -6610,7 +6610,7 @@
         <v>3.05</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6756,7 +6756,7 @@
         <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
         <v>40</v>
@@ -6807,58 +6807,58 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.31</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AV25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AW25" t="n">
         <v>1.31</v>
       </c>
-      <c r="AW25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AX25" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G26" t="n">
         <v>1.92</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7231,16 +7231,16 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="O27" t="n">
         <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
@@ -7255,10 +7255,10 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G28" t="n">
         <v>2.3</v>
@@ -7470,10 +7470,10 @@
         <v>3.3</v>
       </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
         <v>4.6</v>
@@ -7494,7 +7494,7 @@
         <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R28" t="n">
         <v>1.46</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
         <v>1.34</v>
       </c>
       <c r="S31" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
         <v>1.54</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
         <v>2.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R32" t="n">
         <v>1.47</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>6.6</v>
       </c>
       <c r="J33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
         <v>5.8</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
         <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="R34" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="S34" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T34" t="n">
         <v>1.46</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -9529,10 +9529,10 @@
         <v>1.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S36" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9541,10 +9541,10 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -9780,13 +9780,13 @@
         <v>2.94</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R37" t="n">
         <v>1.8</v>
       </c>
       <c r="S37" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T37" t="n">
         <v>1.4</v>
@@ -9906,7 +9906,7 @@
         <v>15</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH37" t="n">
         <v>7.4</v>
@@ -9918,7 +9918,7 @@
         <v>12</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.3</v>
+        <v>2.32</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
@@ -9930,7 +9930,7 @@
         <v>11</v>
       </c>
       <c r="BO37" t="n">
-        <v>4.9</v>
+        <v>2.28</v>
       </c>
       <c r="BP37" t="n">
         <v>36</v>
@@ -9948,7 +9948,7 @@
         <v>7.8</v>
       </c>
       <c r="BU37" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV37" t="n">
         <v>17.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -10019,13 +10019,13 @@
         <v>5.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M38" t="n">
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O38" t="n">
         <v>1.13</v>
@@ -10034,13 +10034,13 @@
         <v>2.86</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R38" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S38" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="T38" t="n">
         <v>1.4</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>6.4</v>
       </c>
       <c r="J39" t="n">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="K39" t="n">
         <v>6.2</v>
@@ -10285,7 +10285,7 @@
         <v>1.13</v>
       </c>
       <c r="P39" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q39" t="n">
         <v>1.33</v>
@@ -10297,13 +10297,13 @@
         <v>1.96</v>
       </c>
       <c r="T39" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U39" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V39" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W39" t="n">
         <v>2.34</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
         <v>1.2</v>
       </c>
       <c r="M41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N41" t="n">
         <v>4.8</v>
@@ -10802,13 +10802,13 @@
         <v>1.51</v>
       </c>
       <c r="S41" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T41" t="n">
         <v>2.04</v>
       </c>
       <c r="U41" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V41" t="n">
         <v>3.6</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -11280,10 +11280,10 @@
         <v>4.9</v>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J43" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K43" t="n">
         <v>3.65</v>
@@ -11301,10 +11301,10 @@
         <v>1.45</v>
       </c>
       <c r="P43" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
@@ -11313,16 +11313,16 @@
         <v>4.6</v>
       </c>
       <c r="T43" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U43" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V43" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W43" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X43" t="n">
         <v>10.5</v>
@@ -11331,7 +11331,7 @@
         <v>14.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA43" t="n">
         <v>170</v>
@@ -11358,7 +11358,7 @@
         <v>24</v>
       </c>
       <c r="AI43" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ43" t="n">
         <v>23</v>
@@ -11373,7 +11373,7 @@
         <v>200</v>
       </c>
       <c r="AN43" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO43" t="n">
         <v>150</v>
@@ -11388,7 +11388,7 @@
         <v>25</v>
       </c>
       <c r="AS43" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT43" t="n">
         <v>6.2</v>
@@ -11400,7 +11400,7 @@
         <v>18.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX43" t="n">
         <v>9.4</v>
@@ -11412,7 +11412,7 @@
         <v>20</v>
       </c>
       <c r="BA43" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB43" t="n">
         <v>19.5</v>
@@ -11424,19 +11424,19 @@
         <v>36</v>
       </c>
       <c r="BE43" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF43" t="n">
         <v>14.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH43" t="n">
         <v>2.96</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="BJ43" t="n">
         <v>11.5</v>
@@ -11481,7 +11481,7 @@
         <v>12</v>
       </c>
       <c r="BX43" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY43" t="n">
         <v>12.5</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -11531,10 +11531,10 @@
         <v>2.84</v>
       </c>
       <c r="H44" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I44" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>3.85</v>
@@ -11558,13 +11558,13 @@
         <v>2.68</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="R44" t="n">
         <v>1.64</v>
       </c>
       <c r="S44" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T44" t="n">
         <v>1.45</v>
@@ -11573,7 +11573,7 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W44" t="n">
         <v>1.54</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
         <v>2.1</v>
       </c>
       <c r="J46" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K46" t="n">
         <v>5</v>
@@ -12057,7 +12057,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="O46" t="n">
         <v>1.11</v>
@@ -12072,7 +12072,7 @@
         <v>1.78</v>
       </c>
       <c r="S46" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="T46" t="n">
         <v>1.45</v>
@@ -12195,16 +12195,16 @@
         <v>1.01</v>
       </c>
       <c r="BH46" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI46" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ46" t="n">
         <v>11.5</v>
       </c>
       <c r="BK46" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
@@ -12216,37 +12216,37 @@
         <v>10.5</v>
       </c>
       <c r="BO46" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BP46" t="n">
         <v>32</v>
       </c>
       <c r="BQ46" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BR46" t="n">
         <v>36</v>
       </c>
       <c r="BS46" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BT46" t="n">
         <v>7.6</v>
       </c>
       <c r="BU46" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BV46" t="n">
         <v>17.5</v>
       </c>
       <c r="BW46" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BX46" t="n">
         <v>26</v>
       </c>
       <c r="BY46" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BZ46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
         <v>3.65</v>
       </c>
       <c r="L48" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
         <v>1.07</v>
@@ -12586,7 +12586,7 @@
         <v>1.76</v>
       </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V48" t="n">
         <v>1.84</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
         <v>2.2</v>
       </c>
       <c r="J49" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K49" t="n">
         <v>3.6</v>
@@ -12819,19 +12819,19 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="O49" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P49" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="R49" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S49" t="n">
         <v>2.58</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
         <v>4.5</v>
       </c>
       <c r="I50" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="n">
         <v>4.7</v>
@@ -13085,19 +13085,19 @@
         <v>1.38</v>
       </c>
       <c r="R50" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="S50" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="T50" t="n">
         <v>1.33</v>
       </c>
       <c r="U50" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W50" t="n">
         <v>2.32</v>
@@ -13157,16 +13157,16 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="AQ50" t="n">
         <v>18.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="AT50" t="n">
         <v>10.5</v>
@@ -13178,7 +13178,7 @@
         <v>12</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="AX50" t="n">
         <v>9.6</v>
@@ -13190,7 +13190,7 @@
         <v>9.6</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="BB50" t="n">
         <v>12</v>
@@ -13202,13 +13202,13 @@
         <v>13.5</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BF50" t="n">
         <v>3.55</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BH50" t="n">
         <v>7.6</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -13306,13 +13306,13 @@
         <v>2.58</v>
       </c>
       <c r="G51" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H51" t="n">
         <v>2.72</v>
       </c>
       <c r="I51" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>3.4</v>
@@ -13321,7 +13321,7 @@
         <v>3.95</v>
       </c>
       <c r="L51" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M51" t="n">
         <v>1.05</v>
@@ -13345,16 +13345,16 @@
         <v>3</v>
       </c>
       <c r="T51" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="U51" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W51" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X51" t="n">
         <v>20</v>
@@ -13465,10 +13465,10 @@
         <v>1.17</v>
       </c>
       <c r="BH51" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="BJ51" t="n">
         <v>12.5</v>
@@ -13480,7 +13480,7 @@
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>3.55</v>
+        <v>1.91</v>
       </c>
       <c r="BN51" t="n">
         <v>7.8</v>
@@ -13492,13 +13492,13 @@
         <v>28</v>
       </c>
       <c r="BQ51" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="BR51" t="n">
         <v>44</v>
       </c>
       <c r="BS51" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="BT51" t="n">
         <v>8</v>
@@ -13510,13 +13510,13 @@
         <v>30</v>
       </c>
       <c r="BW51" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="BX51" t="n">
         <v>44</v>
       </c>
       <c r="BY51" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -13581,7 +13581,7 @@
         <v>1.05</v>
       </c>
       <c r="N52" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O52" t="n">
         <v>1.26</v>
@@ -13593,16 +13593,16 @@
         <v>1.82</v>
       </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S52" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T52" t="n">
         <v>1.58</v>
       </c>
       <c r="U52" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V52" t="n">
         <v>1.36</v>
@@ -13722,7 +13722,7 @@
         <v>1000</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.88</v>
+        <v>1.84</v>
       </c>
       <c r="BJ52" t="n">
         <v>13.5</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G53" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H53" t="n">
         <v>3.65</v>
@@ -13823,208 +13823,208 @@
         <v>4.4</v>
       </c>
       <c r="J53" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K53" t="n">
         <v>4.1</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P53" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BG53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BH53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ53" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN53" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BQ53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR53" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BU53" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV53" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
         <v>3.05</v>
       </c>
       <c r="J54" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
         <v>4.8</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -14325,7 +14325,7 @@
         <v>5.7</v>
       </c>
       <c r="H55" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I55" t="n">
         <v>1.92</v>
@@ -14349,7 +14349,7 @@
         <v>1.33</v>
       </c>
       <c r="P55" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q55" t="n">
         <v>1.98</v>
@@ -14361,10 +14361,10 @@
         <v>3.55</v>
       </c>
       <c r="T55" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U55" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V55" t="n">
         <v>2.08</v>
@@ -14406,7 +14406,7 @@
         <v>25</v>
       </c>
       <c r="AI55" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ55" t="n">
         <v>160</v>
@@ -14451,7 +14451,7 @@
         <v>16</v>
       </c>
       <c r="AX55" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AY55" t="n">
         <v>16</v>
@@ -14469,22 +14469,22 @@
         <v>4.1</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE55" t="n">
         <v>4.2</v>
       </c>
       <c r="BF55" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG55" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH55" t="n">
         <v>3.45</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="BJ55" t="n">
         <v>11</v>
@@ -14502,7 +14502,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BO55" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BP55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -14576,7 +14576,7 @@
         <v>1.77</v>
       </c>
       <c r="G56" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H56" t="n">
         <v>5.7</v>
@@ -14591,16 +14591,16 @@
         <v>3.75</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P56" t="n">
         <v>1.68</v>
@@ -14609,194 +14609,194 @@
         <v>2.28</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BG56" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BK56" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN56" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO56" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BP56" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ56" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT56" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BU56" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BV56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ56" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="CA56" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -14827,40 +14827,40 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G57" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H57" t="n">
         <v>4</v>
       </c>
       <c r="I57" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J57" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="K57" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L57" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M57" t="n">
         <v>1.16</v>
       </c>
       <c r="N57" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="O57" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P57" t="n">
         <v>1.39</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="R57" t="n">
         <v>1.17</v>
@@ -14869,16 +14869,16 @@
         <v>5.3</v>
       </c>
       <c r="T57" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U57" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V57" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W57" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="X57" t="n">
         <v>970</v>
@@ -14911,13 +14911,13 @@
         <v>970</v>
       </c>
       <c r="AH57" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI57" t="n">
         <v>1000</v>
       </c>
       <c r="AJ57" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK57" t="n">
         <v>48</v>
@@ -14929,16 +14929,16 @@
         <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO57" t="n">
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AR57" t="n">
         <v>3.35</v>
@@ -14947,19 +14947,19 @@
         <v>3.6</v>
       </c>
       <c r="AT57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU57" t="n">
         <v>3.3</v>
       </c>
-      <c r="AU57" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AV57" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AW57" t="n">
         <v>3.55</v>
       </c>
       <c r="AX57" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AY57" t="n">
         <v>3.15</v>
@@ -14989,16 +14989,16 @@
         <v>3.6</v>
       </c>
       <c r="BH57" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI57" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ57" t="n">
         <v>1000</v>
       </c>
       <c r="BK57" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BL57" t="n">
         <v>1000</v>
@@ -15016,25 +15016,25 @@
         <v>1000</v>
       </c>
       <c r="BQ57" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BR57" t="n">
         <v>1000</v>
       </c>
       <c r="BS57" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="BT57" t="n">
         <v>1000</v>
       </c>
       <c r="BU57" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BV57" t="n">
         <v>1000</v>
       </c>
       <c r="BW57" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BX57" t="n">
         <v>1000</v>
@@ -15046,11 +15046,11 @@
         <v>1000</v>
       </c>
       <c r="CA57" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="G58" t="n">
         <v>4.3</v>
@@ -15090,7 +15090,7 @@
         <v>2.46</v>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="J58" t="n">
         <v>2.78</v>
@@ -15099,202 +15099,202 @@
         <v>3.25</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P58" t="n">
         <v>1.47</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.46</v>
+        <v>1.53</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BJ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ58" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -15589,85 +15589,85 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="G60" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H60" t="n">
         <v>4.4</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J60" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K60" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L60" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M60" t="n">
         <v>1.1</v>
       </c>
       <c r="N60" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O60" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P60" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R60" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S60" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T60" t="n">
         <v>2.08</v>
       </c>
       <c r="U60" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V60" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W60" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X60" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y60" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA60" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB60" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC60" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD60" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE60" t="n">
         <v>120</v>
       </c>
       <c r="AF60" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG60" t="n">
         <v>13</v>
@@ -15679,43 +15679,43 @@
         <v>130</v>
       </c>
       <c r="AJ60" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK60" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL60" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM60" t="n">
         <v>220</v>
       </c>
       <c r="AN60" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO60" t="n">
         <v>190</v>
       </c>
       <c r="AP60" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AQ60" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR60" t="n">
         <v>4</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AU60" t="n">
         <v>3</v>
       </c>
       <c r="AV60" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW60" t="n">
         <v>4.2</v>
@@ -15742,52 +15742,52 @@
         <v>4.1</v>
       </c>
       <c r="BE60" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF60" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG60" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI60" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ60" t="n">
         <v>12</v>
       </c>
       <c r="BK60" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL60" t="n">
         <v>1000</v>
       </c>
       <c r="BM60" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BN60" t="n">
         <v>4.4</v>
       </c>
       <c r="BO60" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP60" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ60" t="n">
         <v>6</v>
       </c>
       <c r="BR60" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS60" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BT60" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU60" t="n">
         <v>4.8</v>
@@ -15802,17 +15802,17 @@
         <v>1000</v>
       </c>
       <c r="BY60" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BZ60" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA60" t="n">
         <v>2.22</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -15879,10 +15879,10 @@
         <v>1.66</v>
       </c>
       <c r="R61" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S61" t="n">
-        <v>2.68</v>
+        <v>1.67</v>
       </c>
       <c r="T61" t="n">
         <v>1.01</v>
@@ -15891,10 +15891,10 @@
         <v>1.01</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -16005,58 +16005,58 @@
         <v>1.01</v>
       </c>
       <c r="BH61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ61" t="n">
         <v>0</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
         <v>1000</v>
       </c>
       <c r="J62" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K62" t="n">
         <v>1000</v>
@@ -16121,13 +16121,13 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O62" t="n">
         <v>1.29</v>
       </c>
       <c r="P62" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q62" t="n">
         <v>1.31</v>
@@ -16139,10 +16139,10 @@
         <v>1.32</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V62" t="n">
         <v>1.01</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
         <v>2.84</v>
       </c>
       <c r="G63" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H63" t="n">
         <v>2.66</v>
@@ -16384,7 +16384,7 @@
         <v>1.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R63" t="n">
         <v>1.18</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -16608,217 +16608,217 @@
         <v>2.88</v>
       </c>
       <c r="G64" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="H64" t="n">
         <v>2.54</v>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="J64" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K64" t="n">
         <v>3.45</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P64" t="n">
         <v>1.61</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ64" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB64"/>
+  <dimension ref="A1:CB65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,7 +905,7 @@
         <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
         <v>1.44</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.52</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.76</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -1897,22 +1897,22 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
         <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
         <v>1.68</v>
@@ -1921,37 +1921,37 @@
         <v>1.99</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB6" t="n">
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF6" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
@@ -1963,10 +1963,10 @@
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -1975,52 +1975,52 @@
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP6" t="n">
         <v>4.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AU6" t="n">
         <v>5.3</v>
       </c>
       <c r="AV6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AY6" t="n">
-        <v>3.85</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.6</v>
       </c>
       <c r="BD6" t="n">
         <v>4.9</v>
@@ -2029,74 +2029,74 @@
         <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="n">
         <v>3.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BP6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BQ6" t="n">
         <v>4.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY6" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>5.3</v>
       </c>
       <c r="BZ6" t="n">
         <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H7" t="n">
         <v>2.36</v>
@@ -2139,7 +2139,7 @@
         <v>2.48</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
@@ -2148,7 +2148,7 @@
         <v>1.22</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
         <v>6.2</v>
@@ -2178,7 +2178,7 @@
         <v>1.67</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
         <v>36</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I8" t="n">
         <v>3.15</v>
@@ -2402,7 +2402,7 @@
         <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>5.2</v>
@@ -2426,7 +2426,7 @@
         <v>1.56</v>
       </c>
       <c r="U8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V8" t="n">
         <v>1.47</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
         <v>2.84</v>
@@ -2665,7 +2665,7 @@
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
         <v>1.47</v>
@@ -2683,10 +2683,10 @@
         <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
         <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
         <v>1.25</v>
@@ -3445,7 +3445,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -4067,68 +4067,68 @@
         <v>5.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.34</v>
+        <v>5.3</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.34</v>
+        <v>2.54</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.34</v>
+        <v>6.2</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.34</v>
+        <v>4.5</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.34</v>
+        <v>2.42</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.34</v>
+        <v>2.44</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4924,16 @@
         <v>2.78</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H18" t="n">
         <v>2.68</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -4996,7 +4996,7 @@
         <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
         <v>3.7</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
         <v>1.68</v>
       </c>
       <c r="U22" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V22" t="n">
         <v>1.12</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1.97</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,7 +6215,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.28</v>
@@ -6224,13 +6224,13 @@
         <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.92</v>
       </c>
       <c r="G25" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H25" t="n">
         <v>3.8</v>
@@ -6729,13 +6729,13 @@
         <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
         <v>1.76</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
         <v>2.8</v>
@@ -6750,7 +6750,7 @@
         <v>1.29</v>
       </c>
       <c r="W25" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6777,7 +6777,7 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
         <v>1000</v>
@@ -6807,58 +6807,58 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AX25" t="n">
         <v>1.22</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -6983,10 +6983,10 @@
         <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
         <v>1.48</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -7231,22 +7231,22 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O27" t="n">
         <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
         <v>3.3</v>
       </c>
       <c r="I28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>3.5</v>
@@ -7479,16 +7479,16 @@
         <v>4.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
         <v>2.16</v>
@@ -7497,10 +7497,10 @@
         <v>1.71</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T28" t="n">
         <v>1.55</v>
@@ -7515,7 +7515,7 @@
         <v>1.78</v>
       </c>
       <c r="X28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y28" t="n">
         <v>970</v>
@@ -7557,7 +7557,7 @@
         <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
         <v>85</v>
@@ -7566,7 +7566,7 @@
         <v>970</v>
       </c>
       <c r="AO28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP28" t="n">
         <v>1.01</v>
@@ -7581,7 +7581,7 @@
         <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -7596,10 +7596,10 @@
         <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
         <v>1.01</v>
@@ -7617,16 +7617,16 @@
         <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG28" t="n">
         <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="BJ28" t="n">
         <v>12.5</v>
@@ -7641,7 +7641,7 @@
         <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO28" t="n">
         <v>4.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
         <v>1.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="Q30" t="n">
         <v>1.32</v>
@@ -8014,7 +8014,7 @@
         <v>1.41</v>
       </c>
       <c r="U30" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V30" t="n">
         <v>1.24</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
         <v>1.25</v>
       </c>
       <c r="P31" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
         <v>1.73</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
         <v>4.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M32" t="n">
         <v>1.05</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
         <v>1.71</v>
       </c>
       <c r="G34" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="H34" t="n">
         <v>4.1</v>
@@ -8997,7 +8997,7 @@
         <v>5.7</v>
       </c>
       <c r="J34" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K34" t="n">
         <v>4.9</v>
@@ -9009,19 +9009,19 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="O34" t="n">
         <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="R34" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S34" t="n">
         <v>2.3</v>
@@ -9036,7 +9036,7 @@
         <v>1.21</v>
       </c>
       <c r="W34" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="X34" t="n">
         <v>34</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G35" t="n">
         <v>2.22</v>
@@ -9254,7 +9254,7 @@
         <v>4.2</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L35" t="n">
         <v>1.17</v>
@@ -9290,7 +9290,7 @@
         <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X35" t="n">
         <v>55</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>1.81</v>
       </c>
       <c r="G38" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H38" t="n">
         <v>3.8</v>
@@ -10040,7 +10040,7 @@
         <v>1.7</v>
       </c>
       <c r="S38" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T38" t="n">
         <v>1.4</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>6.4</v>
       </c>
       <c r="J39" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="K39" t="n">
         <v>6.2</v>
@@ -10363,7 +10363,7 @@
         <v>38</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ39" t="n">
         <v>4.5</v>
@@ -10396,7 +10396,7 @@
         <v>4</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB39" t="n">
         <v>4.2</v>
@@ -10414,7 +10414,7 @@
         <v>2.88</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH39" t="n">
         <v>7.4</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -10515,13 +10515,13 @@
         <v>2.52</v>
       </c>
       <c r="H40" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K40" t="n">
         <v>4.1</v>
@@ -10557,10 +10557,10 @@
         <v>2.34</v>
       </c>
       <c r="V40" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X40" t="n">
         <v>22</v>
@@ -10686,10 +10686,10 @@
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN40" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO40" t="n">
         <v>4.9</v>
@@ -10698,7 +10698,7 @@
         <v>17</v>
       </c>
       <c r="BQ40" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR40" t="n">
         <v>27</v>
@@ -10707,7 +10707,7 @@
         <v>9.6</v>
       </c>
       <c r="BT40" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU40" t="n">
         <v>5.7</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
         <v>1.51</v>
       </c>
       <c r="S41" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T41" t="n">
         <v>2.04</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -11017,52 +11017,52 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G42" t="n">
         <v>2.6</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I42" t="n">
         <v>3.45</v>
       </c>
       <c r="J42" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K42" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L42" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M42" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="O42" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="P42" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="U42" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="V42" t="n">
         <v>1.4</v>
@@ -11071,10 +11071,10 @@
         <v>1.62</v>
       </c>
       <c r="X42" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Z42" t="n">
         <v>27</v>
@@ -11083,10 +11083,10 @@
         <v>70</v>
       </c>
       <c r="AB42" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD42" t="n">
         <v>17</v>
@@ -11095,13 +11095,13 @@
         <v>48</v>
       </c>
       <c r="AF42" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG42" t="n">
         <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI42" t="n">
         <v>60</v>
@@ -11119,64 +11119,64 @@
         <v>120</v>
       </c>
       <c r="AN42" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AO42" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AR42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT42" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AU42" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX42" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AY42" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF42" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -11304,10 +11304,10 @@
         <v>1.66</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R43" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
         <v>4.6</v>
@@ -11436,7 +11436,7 @@
         <v>2.96</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="BJ43" t="n">
         <v>11.5</v>
@@ -11460,7 +11460,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ43" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BR43" t="n">
         <v>36</v>
@@ -11472,7 +11472,7 @@
         <v>8.4</v>
       </c>
       <c r="BU43" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV43" t="n">
         <v>65</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
         <v>1.17</v>
       </c>
       <c r="P44" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q44" t="n">
         <v>1.49</v>
@@ -11570,7 +11570,7 @@
         <v>1.45</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V44" t="n">
         <v>1.55</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
         <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K45" t="n">
         <v>1000</v>
@@ -11809,10 +11809,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="G46" t="n">
         <v>3.95</v>
@@ -12042,7 +12042,7 @@
         <v>1.88</v>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="J46" t="n">
         <v>4.3</v>
@@ -12057,37 +12057,37 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>1.11</v>
       </c>
       <c r="P46" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="S46" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="T46" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="U46" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="V46" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="W46" t="n">
         <v>1.33</v>
       </c>
       <c r="X46" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Y46" t="n">
         <v>23</v>
@@ -12102,7 +12102,7 @@
         <v>32</v>
       </c>
       <c r="AC46" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD46" t="n">
         <v>15.5</v>
@@ -12111,7 +12111,7 @@
         <v>24</v>
       </c>
       <c r="AF46" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG46" t="n">
         <v>22</v>
@@ -12156,10 +12156,10 @@
         <v>1.01</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
         <v>3.65</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M48" t="n">
         <v>1.07</v>
@@ -12586,7 +12586,7 @@
         <v>1.76</v>
       </c>
       <c r="U48" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="V48" t="n">
         <v>1.84</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -12966,49 +12966,49 @@
         <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BN49" t="n">
         <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BT49" t="n">
         <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BZ49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -13073,28 +13073,28 @@
         <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="O50" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P50" t="n">
         <v>3.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R50" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S50" t="n">
         <v>1.94</v>
       </c>
       <c r="T50" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="U50" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="V50" t="n">
         <v>1.24</v>
@@ -13112,16 +13112,16 @@
         <v>70</v>
       </c>
       <c r="AA50" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB50" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AE50" t="n">
         <v>1000</v>
@@ -13130,85 +13130,85 @@
         <v>23</v>
       </c>
       <c r="AG50" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ50" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AK50" t="n">
         <v>23</v>
       </c>
       <c r="AL50" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AM50" t="n">
         <v>70</v>
       </c>
       <c r="AN50" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.26</v>
+        <v>5.3</v>
       </c>
       <c r="AQ50" t="n">
         <v>18.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.2</v>
+        <v>27</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.26</v>
+        <v>5</v>
       </c>
       <c r="AT50" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AU50" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AV50" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.26</v>
+        <v>5.3</v>
       </c>
       <c r="AX50" t="n">
         <v>9.6</v>
       </c>
       <c r="AY50" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AZ50" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="BB50" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BC50" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BD50" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF50" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="BG50" t="n">
-        <v>2.26</v>
+        <v>19.5</v>
       </c>
       <c r="BH50" t="n">
         <v>7.6</v>
@@ -13226,7 +13226,7 @@
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BN50" t="n">
         <v>7.4</v>
@@ -13238,31 +13238,31 @@
         <v>15</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BR50" t="n">
         <v>25</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BT50" t="n">
         <v>13</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BV50" t="n">
         <v>46</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BX50" t="n">
         <v>46</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BZ50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -13315,7 +13315,7 @@
         <v>3.1</v>
       </c>
       <c r="J51" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K51" t="n">
         <v>3.95</v>
@@ -13526,14 +13526,14 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13548,112 +13548,112 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Sacachispas</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="G52" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="I52" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J52" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="K52" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L52" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>3.15</v>
+        <v>1.08</v>
       </c>
       <c r="O52" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="R52" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="S52" t="n">
-        <v>2.74</v>
+        <v>1.58</v>
       </c>
       <c r="T52" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U52" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X52" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z52" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA52" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC52" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD52" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE52" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF52" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG52" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH52" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI52" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK52" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL52" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM52" t="n">
         <v>1000</v>
@@ -13665,112 +13665,112 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ52" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR52" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="AV52" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW52" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY52" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AZ52" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BA52" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BD52" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ52" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BN52" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP52" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BR52" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BT52" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV52" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BX52" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BZ52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -13797,234 +13797,234 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F53" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P53" t="n">
         <v>2.02</v>
       </c>
-      <c r="G53" t="n">
+      <c r="Q53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U53" t="n">
         <v>2.22</v>
       </c>
-      <c r="H53" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="V53" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X53" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU53" t="n">
         <v>4.4</v>
       </c>
-      <c r="J53" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K53" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="X53" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z53" t="n">
+      <c r="BV53" t="n">
         <v>38</v>
       </c>
-      <c r="AA53" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BG53" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BH53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ53" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN53" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO53" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP53" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR53" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT53" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU53" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV53" t="n">
-        <v>46</v>
-      </c>
       <c r="BW53" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BX53" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -14034,14 +14034,14 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14056,246 +14056,246 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="G54" t="n">
-        <v>2.54</v>
+        <v>2.16</v>
       </c>
       <c r="H54" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="I54" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K54" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L54" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="M54" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="O54" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="P54" t="n">
-        <v>2.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="R54" t="n">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="S54" t="n">
-        <v>2.04</v>
+        <v>2.84</v>
       </c>
       <c r="T54" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="U54" t="n">
-        <v>2.84</v>
+        <v>1.96</v>
       </c>
       <c r="V54" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="W54" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="X54" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="Y54" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Z54" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ54" t="n">
         <v>32</v>
       </c>
-      <c r="AA54" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>40</v>
-      </c>
       <c r="AK54" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL54" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AM54" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN54" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO54" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AQ54" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AR54" t="n">
         <v>19</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AT54" t="n">
-        <v>14</v>
+        <v>2.24</v>
       </c>
       <c r="AU54" t="n">
-        <v>8.4</v>
+        <v>2.16</v>
       </c>
       <c r="AV54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW54" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB54" t="n">
         <v>18.5</v>
       </c>
-      <c r="AX54" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BC54" t="n">
-        <v>15.5</v>
+        <v>2.48</v>
       </c>
       <c r="BD54" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BF54" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="BG54" t="n">
-        <v>9.6</v>
+        <v>2.7</v>
       </c>
       <c r="BH54" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI54" t="n">
-        <v>3.9</v>
+        <v>1.92</v>
       </c>
       <c r="BJ54" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BK54" t="n">
-        <v>6</v>
+        <v>1.67</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>8.6</v>
+        <v>1.92</v>
       </c>
       <c r="BN54" t="n">
         <v>6.4</v>
       </c>
       <c r="BO54" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="BP54" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BQ54" t="n">
-        <v>6.2</v>
+        <v>1.75</v>
       </c>
       <c r="BR54" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="BS54" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="BT54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BU54" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV54" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="BW54" t="n">
-        <v>6.6</v>
+        <v>1.84</v>
       </c>
       <c r="BX54" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>7</v>
+        <v>1.86</v>
       </c>
       <c r="BZ54" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA54" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14305,251 +14305,251 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4.7</v>
+        <v>2.28</v>
       </c>
       <c r="G55" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N55" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X55" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>13</v>
+      </c>
+      <c r="CA55" t="n">
         <v>5.7</v>
       </c>
-      <c r="H55" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K55" t="n">
-        <v>4</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V55" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X55" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG55" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH55" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI55" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ55" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK55" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ55" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT55" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV55" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BW55" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BX55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY55" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA55" t="n">
-        <v>0</v>
-      </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14559,251 +14559,251 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.77</v>
+        <v>4.7</v>
       </c>
       <c r="G56" t="n">
-        <v>1.83</v>
+        <v>5.7</v>
       </c>
       <c r="H56" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X56" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW56" t="n">
         <v>5.7</v>
       </c>
-      <c r="I56" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S56" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X56" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BH56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ56" t="n">
-        <v>17</v>
-      </c>
-      <c r="BK56" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ56" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR56" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS56" t="n">
-        <v>20</v>
-      </c>
-      <c r="BT56" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BU56" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW56" t="n">
-        <v>21</v>
-      </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BZ56" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="CA56" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14818,85 +14818,85 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="G57" t="n">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="H57" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="I57" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="K57" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L57" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="M57" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>2.18</v>
+        <v>2.92</v>
       </c>
       <c r="O57" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="P57" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="R57" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S57" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="T57" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="U57" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V57" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W57" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="X57" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y57" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z57" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AA57" t="n">
         <v>1000</v>
       </c>
       <c r="AB57" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC57" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD57" t="n">
         <v>29</v>
@@ -14905,159 +14905,159 @@
         <v>1000</v>
       </c>
       <c r="AF57" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG57" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AI57" t="n">
         <v>1000</v>
       </c>
       <c r="AJ57" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BZ57" t="n">
         <v>44</v>
       </c>
-      <c r="AK57" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BH57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI57" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BJ57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK57" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BL57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO57" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ57" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BR57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BT57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BV57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BX57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY57" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ57" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA57" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15072,246 +15072,246 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.92</v>
+        <v>2.18</v>
       </c>
       <c r="G58" t="n">
-        <v>4.3</v>
+        <v>2.62</v>
       </c>
       <c r="H58" t="n">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
-        <v>2.84</v>
+        <v>5.4</v>
       </c>
       <c r="J58" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="K58" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X58" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT58" t="n">
         <v>3.25</v>
       </c>
-      <c r="L58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AU58" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH58" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="BI58" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BJ58" t="n">
         <v>1000</v>
       </c>
       <c r="BK58" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BL58" t="n">
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN58" t="n">
         <v>1000</v>
       </c>
       <c r="BO58" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP58" t="n">
         <v>1000</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BR58" t="n">
         <v>1000</v>
       </c>
       <c r="BS58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BT58" t="n">
         <v>1000</v>
       </c>
       <c r="BU58" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BV58" t="n">
         <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BX58" t="n">
         <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA58" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15321,234 +15321,234 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sportivo AC Las Parejas</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Def Belgrano VR</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="G59" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="H59" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I59" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="J59" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="K59" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BJ59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BL59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BN59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BP59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BR59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BT59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BV59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BX59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BZ59" t="n">
         <v>0</v>
@@ -15558,14 +15558,14 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15575,251 +15575,251 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Sportivo AC Las Parejas</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Def Belgrano VR</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G60" t="n">
-        <v>1.95</v>
+        <v>1000</v>
       </c>
       <c r="H60" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J60" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K60" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L60" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="R60" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AK60" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL60" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM60" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="AN60" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO60" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AQ60" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AR60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV60" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AW60" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AX60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AY60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AZ60" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BA60" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BC60" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE60" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BG60" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BH60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BI60" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="BJ60" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK60" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM60" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BN60" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BO60" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BP60" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BQ60" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR60" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS60" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BT60" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BU60" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV60" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BW60" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BX60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BZ60" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA60" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15834,239 +15834,239 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Deportes Rengo Unido</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colchagua CD</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="G61" t="n">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="H61" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="I61" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J61" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="K61" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L61" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M61" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N61" t="n">
-        <v>1.66</v>
+        <v>2.58</v>
       </c>
       <c r="O61" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="P61" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="R61" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V61" t="n">
         <v>1.16</v>
       </c>
-      <c r="S61" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W61" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="X61" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y61" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z61" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA61" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB61" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC61" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD61" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE61" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF61" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG61" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH61" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI61" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK61" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL61" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM61" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN61" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO61" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AU61" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV61" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA61" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BC61" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD61" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF61" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG61" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH61" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI61" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ61" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK61" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL61" t="n">
         <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BN61" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO61" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP61" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ61" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR61" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS61" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BT61" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU61" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV61" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW61" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BX61" t="n">
         <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BZ61" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA61" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -16083,17 +16083,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Concon National FC</t>
+          <t>Deportes Rengo Unido</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportes Colina</t>
+          <t>Colchagua CD</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -16109,7 +16109,7 @@
         <v>1000</v>
       </c>
       <c r="J62" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K62" t="n">
         <v>1000</v>
@@ -16121,28 +16121,28 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="O62" t="n">
         <v>1.29</v>
       </c>
       <c r="P62" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="R62" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S62" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="T62" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U62" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V62" t="n">
         <v>1.01</v>
@@ -16320,14 +16320,14 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16337,114 +16337,114 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Concon National FC</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Deportes Colina</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.84</v>
+        <v>1.02</v>
       </c>
       <c r="G63" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="H63" t="n">
-        <v>2.66</v>
+        <v>1.02</v>
       </c>
       <c r="I63" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J63" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="K63" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L63" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M63" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="O63" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="P63" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.44</v>
+        <v>1.31</v>
       </c>
       <c r="R63" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S63" t="n">
-        <v>4.3</v>
+        <v>2.36</v>
       </c>
       <c r="T63" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="U63" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V63" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="X63" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y63" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z63" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA63" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB63" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC63" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD63" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE63" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF63" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG63" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH63" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI63" t="n">
         <v>1000</v>
       </c>
       <c r="AJ63" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK63" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL63" t="n">
         <v>1000</v>
@@ -16453,135 +16453,135 @@
         <v>1000</v>
       </c>
       <c r="AN63" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO63" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ63" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR63" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS63" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT63" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AU63" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AV63" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW63" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX63" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AY63" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AZ63" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BA63" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB63" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC63" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD63" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="BE63" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="BF63" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG63" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH63" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI63" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BJ63" t="n">
         <v>1000</v>
       </c>
       <c r="BK63" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN63" t="n">
         <v>1000</v>
       </c>
       <c r="BO63" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP63" t="n">
         <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BR63" t="n">
         <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BT63" t="n">
         <v>1000</v>
       </c>
       <c r="BU63" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV63" t="n">
         <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BX63" t="n">
         <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ63" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16596,239 +16596,493 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G64" t="n">
         <v>3.4</v>
       </c>
       <c r="H64" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X64" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK64" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB64" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:37:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Paysandu FC</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Miramar Misiones</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H65" t="n">
         <v>2.54</v>
       </c>
-      <c r="I64" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="I65" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J65" t="n">
         <v>2.94</v>
       </c>
-      <c r="K64" t="n">
+      <c r="K65" t="n">
         <v>3.45</v>
       </c>
-      <c r="L64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N64" t="n">
+      <c r="L65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P65" t="n">
         <v>1.61</v>
       </c>
-      <c r="O64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q64" t="n">
+      <c r="Q65" t="n">
         <v>2.28</v>
       </c>
-      <c r="R64" t="n">
+      <c r="R65" t="n">
         <v>1.14</v>
       </c>
-      <c r="S64" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W64" t="n">
+      <c r="S65" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W65" t="n">
         <v>1.41</v>
       </c>
-      <c r="X64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB64" t="inlineStr">
-        <is>
-          <t>2026-06-25 16:22:34</t>
+      <c r="X65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB65" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -896,7 +896,7 @@
         <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.79</v>
@@ -908,7 +908,7 @@
         <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -962,7 +962,7 @@
         <v>42</v>
       </c>
       <c r="AO2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
         <v>4</v>
@@ -974,7 +974,7 @@
         <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
         <v>4</v>
@@ -983,37 +983,37 @@
         <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
         <v>5</v>
       </c>
       <c r="BE2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF2" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.7</v>
       </c>
       <c r="BG2" t="n">
         <v>4.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
         <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q4" t="n">
         <v>1.55</v>
@@ -1404,7 +1404,7 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1416,7 +1416,7 @@
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
         <v>1.43</v>
@@ -1667,7 +1667,7 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H6" t="n">
         <v>2.88</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -1912,7 +1912,7 @@
         <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="T6" t="n">
         <v>1.68</v>
@@ -1921,10 +1921,10 @@
         <v>1.99</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
         <v>2.38</v>
       </c>
       <c r="I7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J7" t="n">
         <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.21</v>
@@ -2175,10 +2175,10 @@
         <v>2.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X7" t="n">
         <v>36</v>
@@ -2235,7 +2235,7 @@
         <v>10.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>15.5</v>
@@ -2244,7 +2244,7 @@
         <v>17.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
         <v>17.5</v>
@@ -2271,16 +2271,16 @@
         <v>18.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
         <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
         <v>13</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -2393,10 +2393,10 @@
         <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.26</v>
@@ -2429,7 +2429,7 @@
         <v>2.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
         <v>1.68</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>2.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H9" t="n">
         <v>2.84</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J9" t="n">
         <v>3.1</v>
@@ -2671,10 +2671,10 @@
         <v>1.47</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
         <v>1.47</v>
@@ -2683,10 +2683,10 @@
         <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2740,55 +2740,55 @@
         <v>12</v>
       </c>
       <c r="AO9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>3.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW9" t="n">
         <v>4.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
         <v>4.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
         <v>3.55</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>1.9</v>
       </c>
       <c r="H10" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
         <v>5.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -3678,13 +3678,13 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P13" t="n">
         <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>1.33</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G19" t="n">
         <v>4.7</v>
@@ -5184,13 +5184,13 @@
         <v>1.82</v>
       </c>
       <c r="I19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.27</v>
@@ -5223,7 +5223,7 @@
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="W19" t="n">
         <v>1.27</v>
@@ -5280,7 +5280,7 @@
         <v>48</v>
       </c>
       <c r="AO19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP19" t="n">
         <v>6.4</v>
@@ -5319,16 +5319,16 @@
         <v>6.8</v>
       </c>
       <c r="BB19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE19" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
         <v>7.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
         <v>2.32</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.37</v>
@@ -5453,28 +5453,28 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V20" t="n">
         <v>1.38</v>
@@ -5483,7 +5483,7 @@
         <v>1.75</v>
       </c>
       <c r="X20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
         <v>16.5</v>
@@ -5495,7 +5495,7 @@
         <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
         <v>10</v>
@@ -5507,10 +5507,10 @@
         <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
         <v>20</v>
@@ -5519,7 +5519,7 @@
         <v>50</v>
       </c>
       <c r="AJ20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK20" t="n">
         <v>29</v>
@@ -5531,7 +5531,7 @@
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
         <v>36</v>
@@ -5540,22 +5540,22 @@
         <v>13.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
         <v>30</v>
@@ -5564,28 +5564,28 @@
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
         <v>36</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG20" t="n">
         <v>24</v>
@@ -5600,22 +5600,22 @@
         <v>9.6</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO20" t="n">
         <v>4</v>
       </c>
       <c r="BP20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ20" t="n">
         <v>6.4</v>
@@ -5624,7 +5624,7 @@
         <v>30</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT20" t="n">
         <v>7</v>
@@ -5636,23 +5636,23 @@
         <v>27</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX20" t="n">
         <v>38</v>
       </c>
       <c r="BY20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ20" t="n">
         <v>25</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
         <v>1.43</v>
@@ -5707,7 +5707,7 @@
         <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="O21" t="n">
         <v>1.48</v>
@@ -5812,7 +5812,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX21" t="n">
         <v>9.6</v>
@@ -5824,7 +5824,7 @@
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -5833,13 +5833,13 @@
         <v>5.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF21" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BG21" t="n">
         <v>6</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
         <v>8.4</v>
       </c>
       <c r="I22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -5982,7 +5982,7 @@
         <v>1.7</v>
       </c>
       <c r="U22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V22" t="n">
         <v>1.12</v>
@@ -6039,19 +6039,19 @@
         <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AO22" t="n">
         <v>95</v>
       </c>
       <c r="AP22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>5.5</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AR22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS22" t="n">
         <v>5.5</v>
@@ -6063,10 +6063,10 @@
         <v>13</v>
       </c>
       <c r="AV22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW22" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.5</v>
       </c>
       <c r="AX22" t="n">
         <v>10.5</v>
@@ -6087,16 +6087,16 @@
         <v>12</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF22" t="n">
         <v>3.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1.97</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,10 +6215,10 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
         <v>1.25</v>
@@ -6230,7 +6230,7 @@
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G25" t="n">
         <v>2.04</v>
@@ -6708,13 +6708,13 @@
         <v>3.85</v>
       </c>
       <c r="I25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6729,7 +6729,7 @@
         <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
         <v>1.78</v>
@@ -6738,7 +6738,7 @@
         <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T25" t="n">
         <v>1.69</v>
@@ -6747,7 +6747,7 @@
         <v>2.18</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
         <v>1.96</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -6959,16 +6959,16 @@
         <v>1.92</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
         <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6986,10 +6986,10 @@
         <v>2.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
         <v>2.66</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="O27" t="n">
         <v>1.36</v>
@@ -7240,13 +7240,13 @@
         <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H28" t="n">
         <v>3.3</v>
       </c>
       <c r="I28" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J28" t="n">
         <v>3.6</v>
@@ -7500,7 +7500,7 @@
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T28" t="n">
         <v>1.55</v>
@@ -7512,7 +7512,7 @@
         <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X28" t="n">
         <v>22</v>
@@ -7596,7 +7596,7 @@
         <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28" t="n">
         <v>1.01</v>
@@ -7623,10 +7623,10 @@
         <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
@@ -7638,7 +7638,7 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="BN28" t="n">
         <v>5.3</v>
@@ -7650,31 +7650,31 @@
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.83</v>
+        <v>2.66</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
         <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
         <v>1.6</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>13</v>
       </c>
       <c r="J30" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>2.66</v>
       </c>
       <c r="O30" t="n">
         <v>1.1</v>
       </c>
       <c r="P30" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Q30" t="n">
         <v>1.11</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="T30" t="n">
         <v>1.18</v>
@@ -8020,7 +8020,7 @@
         <v>1.08</v>
       </c>
       <c r="W30" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
         <v>25</v>
       </c>
       <c r="AG31" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH31" t="n">
         <v>970</v>
@@ -8337,7 +8337,7 @@
         <v>3.7</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS31" t="n">
         <v>4.5</v>
@@ -8346,13 +8346,13 @@
         <v>3.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AV31" t="n">
         <v>3.7</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX31" t="n">
         <v>4.2</v>
@@ -8361,7 +8361,7 @@
         <v>3.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BA31" t="n">
         <v>4.5</v>
@@ -8373,10 +8373,10 @@
         <v>4.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF31" t="n">
         <v>4.3</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
         <v>2.34</v>
       </c>
       <c r="V32" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W32" t="n">
         <v>1.5</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G33" t="n">
         <v>1.65</v>
@@ -8743,10 +8743,10 @@
         <v>6.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="K33" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L33" t="n">
         <v>1.26</v>
@@ -8755,7 +8755,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.17</v>
@@ -8770,7 +8770,7 @@
         <v>1.56</v>
       </c>
       <c r="S33" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T33" t="n">
         <v>1.62</v>
@@ -8782,7 +8782,7 @@
         <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X33" t="n">
         <v>32</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -8985,13 +8985,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G34" t="n">
         <v>1.8</v>
       </c>
       <c r="H34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I34" t="n">
         <v>5</v>
@@ -9000,28 +9000,28 @@
         <v>4.2</v>
       </c>
       <c r="K34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P34" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R34" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S34" t="n">
         <v>2.36</v>
@@ -9030,7 +9030,7 @@
         <v>1.59</v>
       </c>
       <c r="U34" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V34" t="n">
         <v>1.25</v>
@@ -9045,7 +9045,7 @@
         <v>28</v>
       </c>
       <c r="Z34" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA34" t="n">
         <v>110</v>
@@ -9075,7 +9075,7 @@
         <v>55</v>
       </c>
       <c r="AJ34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK34" t="n">
         <v>17.5</v>
@@ -9087,7 +9087,7 @@
         <v>80</v>
       </c>
       <c r="AN34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO34" t="n">
         <v>44</v>
@@ -9150,7 +9150,7 @@
         <v>4.7</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ34" t="n">
         <v>9.4</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -9239,31 +9239,31 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G35" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H35" t="n">
         <v>3.1</v>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J35" t="n">
         <v>4.3</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L35" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M35" t="n">
         <v>1.02</v>
       </c>
       <c r="N35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O35" t="n">
         <v>1.12</v>
@@ -9281,25 +9281,25 @@
         <v>1.86</v>
       </c>
       <c r="T35" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U35" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W35" t="n">
         <v>1.83</v>
       </c>
       <c r="X35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y35" t="n">
         <v>34</v>
       </c>
       <c r="Z35" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA35" t="n">
         <v>70</v>
@@ -9311,7 +9311,7 @@
         <v>15.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE35" t="n">
         <v>36</v>
@@ -9353,7 +9353,7 @@
         <v>19.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS35" t="n">
         <v>4.1</v>
@@ -9392,10 +9392,10 @@
         <v>16</v>
       </c>
       <c r="BE35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG35" t="n">
         <v>10</v>
@@ -9404,7 +9404,7 @@
         <v>5.7</v>
       </c>
       <c r="BI35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ35" t="n">
         <v>8.4</v>
@@ -9431,7 +9431,7 @@
         <v>6</v>
       </c>
       <c r="BR35" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="BS35" t="n">
         <v>6.8</v>
@@ -9443,7 +9443,7 @@
         <v>5.6</v>
       </c>
       <c r="BV35" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
         <v>7.2</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -9526,13 +9526,13 @@
         <v>1.13</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S36" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -9753,16 +9753,16 @@
         <v>4.2</v>
       </c>
       <c r="H37" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I37" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="J37" t="n">
         <v>4.2</v>
       </c>
       <c r="K37" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9783,10 +9783,10 @@
         <v>1.41</v>
       </c>
       <c r="R37" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S37" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T37" t="n">
         <v>1.45</v>
@@ -9795,10 +9795,10 @@
         <v>2.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X37" t="n">
         <v>44</v>
@@ -9813,7 +9813,7 @@
         <v>29</v>
       </c>
       <c r="AB37" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AC37" t="n">
         <v>14</v>
@@ -9867,7 +9867,7 @@
         <v>17</v>
       </c>
       <c r="AT37" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
         <v>8.6</v>
@@ -9903,7 +9903,7 @@
         <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
         <v>6</v>
@@ -9918,7 +9918,7 @@
         <v>12</v>
       </c>
       <c r="BK37" t="n">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
@@ -9930,7 +9930,7 @@
         <v>11</v>
       </c>
       <c r="BO37" t="n">
-        <v>2.28</v>
+        <v>4.9</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
@@ -9948,7 +9948,7 @@
         <v>7.8</v>
       </c>
       <c r="BU37" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BV37" t="n">
         <v>18</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -10007,10 +10007,10 @@
         <v>1.96</v>
       </c>
       <c r="H38" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J38" t="n">
         <v>4.3</v>
@@ -10028,139 +10028,139 @@
         <v>6.2</v>
       </c>
       <c r="O38" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P38" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="R38" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T38" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="U38" t="n">
-        <v>2.16</v>
+        <v>2.68</v>
       </c>
       <c r="V38" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W38" t="n">
         <v>2.04</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD38" t="n">
         <v>22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF38" t="n">
         <v>19.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH38" t="n">
         <v>19</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN38" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP38" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R39" t="n">
         <v>1.84</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -10509,13 +10509,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G40" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H40" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I40" t="n">
         <v>3.1</v>
@@ -10524,7 +10524,7 @@
         <v>3.65</v>
       </c>
       <c r="K40" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L40" t="n">
         <v>1.35</v>
@@ -10533,34 +10533,34 @@
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O40" t="n">
         <v>1.26</v>
       </c>
       <c r="P40" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R40" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S40" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T40" t="n">
         <v>1.65</v>
       </c>
       <c r="U40" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V40" t="n">
         <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X40" t="n">
         <v>22</v>
@@ -10599,10 +10599,10 @@
         <v>44</v>
       </c>
       <c r="AJ40" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL40" t="n">
         <v>40</v>
@@ -10626,7 +10626,7 @@
         <v>19.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT40" t="n">
         <v>11</v>
@@ -10638,7 +10638,7 @@
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX40" t="n">
         <v>15</v>
@@ -10650,19 +10650,19 @@
         <v>14</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC40" t="n">
         <v>21</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF40" t="n">
         <v>14.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -10766,16 +10766,16 @@
         <v>10.5</v>
       </c>
       <c r="G41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="H41" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I41" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J41" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K41" t="n">
         <v>6.2</v>
@@ -10787,139 +10787,139 @@
         <v>1.04</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O41" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P41" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R41" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S41" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="T41" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U41" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="V41" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA41" t="n">
         <v>11</v>
       </c>
-      <c r="Z41" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AB41" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC41" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE41" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AH41" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ41" t="n">
         <v>520</v>
       </c>
       <c r="AK41" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AL41" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM41" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AP41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ41" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS41" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT41" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AU41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW41" t="n">
         <v>12.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="AY41" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="AZ41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.8</v>
+        <v>90</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.8</v>
+        <v>44</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.7</v>
+        <v>42</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.8</v>
+        <v>46</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.8</v>
+        <v>48</v>
       </c>
       <c r="BG41" t="n">
         <v>4.7</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -11442,13 +11442,13 @@
         <v>11.5</v>
       </c>
       <c r="BK43" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN43" t="n">
         <v>4.4</v>
@@ -11460,7 +11460,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ43" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR43" t="n">
         <v>36</v>
@@ -11469,7 +11469,7 @@
         <v>11</v>
       </c>
       <c r="BT43" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU43" t="n">
         <v>5.5</v>
@@ -11478,23 +11478,23 @@
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>2.78</v>
       </c>
       <c r="J44" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K44" t="n">
         <v>4.6</v>
@@ -11555,16 +11555,16 @@
         <v>1.16</v>
       </c>
       <c r="P44" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="R44" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S44" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T44" t="n">
         <v>1.48</v>
@@ -11582,7 +11582,7 @@
         <v>34</v>
       </c>
       <c r="Y44" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z44" t="n">
         <v>26</v>
@@ -11627,7 +11627,7 @@
         <v>60</v>
       </c>
       <c r="AN44" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO44" t="n">
         <v>15</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
         <v>1.02</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O46" t="n">
         <v>1.11</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -12565,7 +12565,7 @@
         <v>1.07</v>
       </c>
       <c r="N48" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O48" t="n">
         <v>1.32</v>
@@ -12583,7 +12583,7 @@
         <v>3.6</v>
       </c>
       <c r="T48" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U48" t="n">
         <v>2.06</v>
@@ -12616,7 +12616,7 @@
         <v>11.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF48" t="n">
         <v>34</v>
@@ -12628,7 +12628,7 @@
         <v>19.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ48" t="n">
         <v>85</v>
@@ -12673,7 +12673,7 @@
         <v>19.5</v>
       </c>
       <c r="AX48" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY48" t="n">
         <v>13.5</v>
@@ -12682,19 +12682,19 @@
         <v>15.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB48" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC48" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC48" t="n">
-        <v>7</v>
-      </c>
       <c r="BD48" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF48" t="n">
         <v>40</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -12795,22 +12795,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H49" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="J49" t="n">
         <v>3.05</v>
       </c>
       <c r="K49" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -12819,16 +12819,16 @@
         <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O49" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R49" t="n">
         <v>1.2</v>
@@ -12837,28 +12837,28 @@
         <v>4.8</v>
       </c>
       <c r="T49" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U49" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V49" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="W49" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X49" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z49" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y49" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>14</v>
-      </c>
       <c r="AA49" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB49" t="n">
         <v>15</v>
@@ -12900,61 +12900,61 @@
         <v>150</v>
       </c>
       <c r="AO49" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AR49" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AU49" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="AV49" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AW49" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX49" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AY49" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ49" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB49" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH49" t="n">
         <v>3.25</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>1.65</v>
       </c>
       <c r="G50" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H50" t="n">
         <v>4.5</v>
@@ -13076,7 +13076,7 @@
         <v>7.2</v>
       </c>
       <c r="O50" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P50" t="n">
         <v>3.2</v>
@@ -13085,25 +13085,25 @@
         <v>1.39</v>
       </c>
       <c r="R50" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S50" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T50" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U50" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="V50" t="n">
         <v>1.24</v>
       </c>
       <c r="W50" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X50" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y50" t="n">
         <v>38</v>
@@ -13118,16 +13118,16 @@
         <v>21</v>
       </c>
       <c r="AC50" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD50" t="n">
         <v>25</v>
       </c>
       <c r="AE50" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF50" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG50" t="n">
         <v>14</v>
@@ -13136,7 +13136,7 @@
         <v>16.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ50" t="n">
         <v>19.5</v>
@@ -13148,25 +13148,25 @@
         <v>23</v>
       </c>
       <c r="AM50" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN50" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AO50" t="n">
         <v>34</v>
       </c>
       <c r="AP50" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR50" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AS50" t="n">
         <v>5</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>5.2</v>
       </c>
       <c r="AT50" t="n">
         <v>12.5</v>
@@ -13178,7 +13178,7 @@
         <v>14.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX50" t="n">
         <v>11.5</v>
@@ -13190,7 +13190,7 @@
         <v>14</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB50" t="n">
         <v>14</v>
@@ -13202,13 +13202,13 @@
         <v>16</v>
       </c>
       <c r="BE50" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="BF50" t="n">
         <v>4.1</v>
       </c>
       <c r="BG50" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH50" t="n">
         <v>7.6</v>
@@ -13226,7 +13226,7 @@
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BN50" t="n">
         <v>7.4</v>
@@ -13244,7 +13244,7 @@
         <v>25</v>
       </c>
       <c r="BS50" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BT50" t="n">
         <v>13</v>
@@ -13256,13 +13256,13 @@
         <v>46</v>
       </c>
       <c r="BW50" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BX50" t="n">
         <v>46</v>
       </c>
       <c r="BY50" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BZ50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -13303,22 +13303,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G51" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H51" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J51" t="n">
         <v>3.45</v>
       </c>
       <c r="K51" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L51" t="n">
         <v>1.14</v>
@@ -13327,37 +13327,37 @@
         <v>1.06</v>
       </c>
       <c r="N51" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O51" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R51" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S51" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T51" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U51" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V51" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W51" t="n">
         <v>1.55</v>
       </c>
       <c r="X51" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y51" t="n">
         <v>13</v>
@@ -13372,7 +13372,7 @@
         <v>12.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD51" t="n">
         <v>15.5</v>
@@ -13420,7 +13420,7 @@
         <v>16.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT51" t="n">
         <v>10.5</v>
@@ -13432,7 +13432,7 @@
         <v>11</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX51" t="n">
         <v>15.5</v>
@@ -13444,19 +13444,19 @@
         <v>14</v>
       </c>
       <c r="BA51" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC51" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD51" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF51" t="n">
         <v>16.5</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="G52" t="n">
         <v>2.38</v>
@@ -13569,7 +13569,7 @@
         <v>990</v>
       </c>
       <c r="J52" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="K52" t="n">
         <v>950</v>
@@ -13590,7 +13590,7 @@
         <v>1.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R52" t="n">
         <v>1.08</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G53" t="n">
         <v>2.34</v>
@@ -13820,7 +13820,7 @@
         <v>3.3</v>
       </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J53" t="n">
         <v>3.65</v>
@@ -13829,13 +13829,13 @@
         <v>3.9</v>
       </c>
       <c r="L53" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M53" t="n">
         <v>1.06</v>
       </c>
       <c r="N53" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
         <v>1.28</v>
@@ -13850,16 +13850,16 @@
         <v>1.4</v>
       </c>
       <c r="S53" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T53" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U53" t="n">
         <v>2.22</v>
       </c>
       <c r="V53" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W53" t="n">
         <v>1.74</v>
@@ -13916,7 +13916,7 @@
         <v>19.5</v>
       </c>
       <c r="AO53" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP53" t="n">
         <v>14</v>
@@ -13952,7 +13952,7 @@
         <v>14</v>
       </c>
       <c r="BA53" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB53" t="n">
         <v>4.8</v>
@@ -13961,7 +13961,7 @@
         <v>19.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE53" t="n">
         <v>5.3</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
         <v>3.55</v>
       </c>
       <c r="K54" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
         <v>2.28</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H55" t="n">
         <v>2.66</v>
@@ -14370,7 +14370,7 @@
         <v>1.49</v>
       </c>
       <c r="W55" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X55" t="n">
         <v>42</v>
@@ -14421,7 +14421,7 @@
         <v>55</v>
       </c>
       <c r="AN55" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO55" t="n">
         <v>16</v>
@@ -14433,7 +14433,7 @@
         <v>15.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS55" t="n">
         <v>1.01</v>
@@ -14481,7 +14481,7 @@
         <v>9.6</v>
       </c>
       <c r="BH55" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI55" t="n">
         <v>3.9</v>
@@ -14496,7 +14496,7 @@
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN55" t="n">
         <v>6.4</v>
@@ -14508,7 +14508,7 @@
         <v>16</v>
       </c>
       <c r="BQ55" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR55" t="n">
         <v>22</v>
@@ -14526,23 +14526,23 @@
         <v>19</v>
       </c>
       <c r="BW55" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX55" t="n">
         <v>24</v>
       </c>
       <c r="BY55" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ55" t="n">
         <v>13</v>
       </c>
       <c r="CA55" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -14573,25 +14573,25 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G56" t="n">
         <v>5.7</v>
       </c>
       <c r="H56" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I56" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J56" t="n">
         <v>3.7</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L56" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M56" t="n">
         <v>1.07</v>
@@ -14603,10 +14603,10 @@
         <v>1.33</v>
       </c>
       <c r="P56" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R56" t="n">
         <v>1.31</v>
@@ -14615,7 +14615,7 @@
         <v>3.55</v>
       </c>
       <c r="T56" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U56" t="n">
         <v>1.92</v>
@@ -14681,7 +14681,7 @@
         <v>16.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ56" t="n">
         <v>7</v>
@@ -14693,7 +14693,7 @@
         <v>16</v>
       </c>
       <c r="AT56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU56" t="n">
         <v>7.4</v>
@@ -14702,7 +14702,7 @@
         <v>8.6</v>
       </c>
       <c r="AW56" t="n">
-        <v>14.5</v>
+        <v>3.7</v>
       </c>
       <c r="AX56" t="n">
         <v>3.95</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -14869,7 +14869,7 @@
         <v>4.4</v>
       </c>
       <c r="T57" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U57" t="n">
         <v>1.76</v>
@@ -14878,7 +14878,7 @@
         <v>1.2</v>
       </c>
       <c r="W57" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X57" t="n">
         <v>13</v>
@@ -15010,7 +15010,7 @@
         <v>5.5</v>
       </c>
       <c r="BO57" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BP57" t="n">
         <v>18</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -15882,7 +15882,7 @@
         <v>1.24</v>
       </c>
       <c r="S61" t="n">
-        <v>3.95</v>
+        <v>1.05</v>
       </c>
       <c r="T61" t="n">
         <v>2.08</v>
@@ -16008,7 +16008,7 @@
         <v>3.1</v>
       </c>
       <c r="BI61" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="BJ61" t="n">
         <v>12</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -16375,22 +16375,22 @@
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="O63" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="P63" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R63" t="n">
         <v>1.16</v>
       </c>
       <c r="S63" t="n">
-        <v>2.36</v>
+        <v>1.32</v>
       </c>
       <c r="T63" t="n">
         <v>1.11</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -1019,68 +1019,68 @@
         <v>4.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,19 +1135,19 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q3" t="n">
         <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
         <v>1.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
         <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.55</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.43</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
         <v>2.88</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -1921,10 +1921,10 @@
         <v>1.99</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
         <v>2.38</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>3.95</v>
@@ -2172,13 +2172,13 @@
         <v>1.47</v>
       </c>
       <c r="U7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>36</v>
@@ -2193,22 +2193,22 @@
         <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
         <v>13</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15</v>
       </c>
       <c r="AE7" t="n">
         <v>26</v>
       </c>
       <c r="AF7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>14.5</v>
@@ -2217,34 +2217,34 @@
         <v>32</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>17.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT7" t="n">
         <v>17.5</v>
@@ -2253,7 +2253,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -2271,22 +2271,22 @@
         <v>18.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH7" t="n">
         <v>5</v>
@@ -2298,59 +2298,59 @@
         <v>8.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
         <v>25</v>
       </c>
       <c r="BS7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV7" t="n">
         <v>15.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
         <v>22</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>14</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
         <v>2.46</v>
@@ -2405,10 +2405,10 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
         <v>2.46</v>
@@ -2417,31 +2417,31 @@
         <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T8" t="n">
         <v>1.56</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
         <v>1.68</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
         <v>55</v>
@@ -2450,7 +2450,7 @@
         <v>15</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
@@ -2459,13 +2459,13 @@
         <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI8" t="n">
         <v>40</v>
@@ -2480,13 +2480,13 @@
         <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
@@ -2498,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -2510,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX8" t="n">
         <v>16</v>
@@ -2522,19 +2522,19 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
         <v>19.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
@@ -2546,7 +2546,7 @@
         <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.6</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
         <v>5.8</v>
@@ -2576,7 +2576,7 @@
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
         <v>6.6</v>
@@ -2591,7 +2591,7 @@
         <v>8.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY8" t="n">
         <v>9.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
         <v>2.84</v>
       </c>
       <c r="I9" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
         <v>4.8</v>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
         <v>1.47</v>
@@ -2683,10 +2683,10 @@
         <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2797,68 +2797,68 @@
         <v>4.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.1</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.79</v>
+        <v>3.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="BN9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BT9" t="n">
         <v>7.6</v>
       </c>
-      <c r="BO9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BU9" t="n">
-        <v>1.73</v>
+        <v>3.55</v>
       </c>
       <c r="BV9" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="BX9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.91</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
         <v>1.9</v>
@@ -2898,16 +2898,16 @@
         <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
         <v>4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
@@ -2937,7 +2937,7 @@
         <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
         <v>2.1</v>
@@ -2949,7 +2949,7 @@
         <v>27</v>
       </c>
       <c r="Z10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>110</v>
@@ -2997,7 +2997,7 @@
         <v>46</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ10" t="n">
         <v>4.2</v>
@@ -3006,31 +3006,31 @@
         <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
         <v>3.75</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
         <v>3.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>3.95</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB10" t="n">
         <v>4.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3143,64 +3143,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="G11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.24</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="X11" t="n">
         <v>30</v>
       </c>
       <c r="Y11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z11" t="n">
         <v>75</v>
@@ -3215,7 +3215,7 @@
         <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE11" t="n">
         <v>110</v>
@@ -3233,10 +3233,10 @@
         <v>90</v>
       </c>
       <c r="AJ11" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
@@ -3251,122 +3251,122 @@
         <v>110</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW11" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AX11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY11" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.55</v>
       </c>
       <c r="AZ11" t="n">
         <v>4.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BD11" t="n">
         <v>4.4</v>
       </c>
       <c r="BE11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH11" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BI11" t="n">
         <v>2.86</v>
       </c>
-      <c r="BG11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
         <v>3.95</v>
@@ -3953,10 +3953,10 @@
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X14" t="n">
         <v>15.5</v>
@@ -3965,7 +3965,7 @@
         <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
         <v>110</v>
@@ -3992,7 +3992,7 @@
         <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ14" t="n">
         <v>26</v>
@@ -4013,7 +4013,7 @@
         <v>75</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ14" t="n">
         <v>5</v>
@@ -4031,7 +4031,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW14" t="n">
         <v>6.6</v>
@@ -4043,7 +4043,7 @@
         <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA14" t="n">
         <v>6.8</v>
@@ -4061,13 +4061,13 @@
         <v>7</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG14" t="n">
         <v>6.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI14" t="n">
         <v>2.74</v>
@@ -4076,7 +4076,7 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4085,25 +4085,25 @@
         <v>2.54</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU14" t="n">
         <v>4.5</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="G16" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="H16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I16" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.37</v>
@@ -4443,10 +4443,10 @@
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1.89</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.88</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
@@ -4458,37 +4458,37 @@
         <v>2.06</v>
       </c>
       <c r="U16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z16" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA16" t="n">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="AB16" t="n">
         <v>8.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE16" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF16" t="n">
         <v>9.4</v>
@@ -4500,7 +4500,7 @@
         <v>32</v>
       </c>
       <c r="AI16" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="n">
         <v>14.5</v>
@@ -4512,76 +4512,76 @@
         <v>48</v>
       </c>
       <c r="AM16" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO16" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>4.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV16" t="n">
         <v>5.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK16" t="n">
         <v>5.7</v>
@@ -4590,28 +4590,28 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.61</v>
+        <v>2.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BP16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR16" t="n">
         <v>28</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU16" t="n">
         <v>5.7</v>
@@ -4629,14 +4629,14 @@
         <v>2.66</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G17" t="n">
         <v>3.4</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="I17" t="n">
         <v>2.98</v>
@@ -4682,215 +4682,215 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="P17" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q17" t="n">
         <v>2.38</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -5193,49 +5193,49 @@
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
         <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA19" t="n">
         <v>22</v>
@@ -5244,7 +5244,7 @@
         <v>21</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -5253,43 +5253,43 @@
         <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH19" t="n">
         <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
         <v>60</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS19" t="n">
         <v>17.5</v>
@@ -5298,7 +5298,7 @@
         <v>17</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV19" t="n">
         <v>9.199999999999999</v>
@@ -5307,7 +5307,7 @@
         <v>15</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AY19" t="n">
         <v>15</v>
@@ -5316,43 +5316,43 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BB19" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BG19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH19" t="n">
         <v>4.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN19" t="n">
         <v>8.4</v>
@@ -5364,7 +5364,7 @@
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
         <v>12.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX19" t="n">
         <v>24</v>
@@ -5391,14 +5391,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA19" t="n">
         <v>6.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G20" t="n">
         <v>2.32</v>
@@ -5438,7 +5438,7 @@
         <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.55</v>
@@ -5453,43 +5453,43 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.38</v>
       </c>
       <c r="W20" t="n">
         <v>1.75</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="n">
         <v>70</v>
@@ -5501,7 +5501,7 @@
         <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>40</v>
@@ -5513,7 +5513,7 @@
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI20" t="n">
         <v>50</v>
@@ -5522,34 +5522,34 @@
         <v>32</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
         <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO20" t="n">
         <v>36</v>
       </c>
       <c r="AP20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
@@ -5573,22 +5573,22 @@
         <v>36</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.8</v>
+        <v>19.5</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="BF20" t="n">
         <v>14.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BH20" t="n">
         <v>3.7</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G21" t="n">
         <v>2.08</v>
@@ -5692,13 +5692,13 @@
         <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.43</v>
@@ -5707,13 +5707,13 @@
         <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>1.48</v>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
         <v>2.42</v>
@@ -5737,10 +5737,10 @@
         <v>1.92</v>
       </c>
       <c r="X21" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
         <v>42</v>
@@ -5752,10 +5752,10 @@
         <v>7.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
         <v>95</v>
@@ -5764,7 +5764,7 @@
         <v>11.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
         <v>29</v>
@@ -5794,13 +5794,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT21" t="n">
         <v>6.2</v>
@@ -5809,10 +5809,10 @@
         <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX21" t="n">
         <v>9.6</v>
@@ -5824,25 +5824,25 @@
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
         <v>18.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH21" t="n">
         <v>2.96</v>
@@ -5854,7 +5854,7 @@
         <v>12</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5866,13 +5866,13 @@
         <v>4.6</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BP21" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
@@ -5884,7 +5884,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>1.39</v>
       </c>
       <c r="H22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I22" t="n">
         <v>9.199999999999999</v>
@@ -5955,7 +5955,7 @@
         <v>6.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
@@ -5970,16 +5970,16 @@
         <v>3.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R22" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S22" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U22" t="n">
         <v>2.32</v>
@@ -5997,10 +5997,10 @@
         <v>55</v>
       </c>
       <c r="Z22" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
         <v>17.5</v>
@@ -6012,7 +6012,7 @@
         <v>40</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
         <v>14.5</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="AI22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>15.5</v>
@@ -6036,37 +6036,37 @@
         <v>32</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
         <v>3.9</v>
       </c>
       <c r="AO22" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.4</v>
+        <v>24</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.5</v>
+        <v>26</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
         <v>10.5</v>
@@ -6075,10 +6075,10 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.5</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
         <v>11.5</v>
@@ -6087,80 +6087,80 @@
         <v>12</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="BF22" t="n">
         <v>3.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.36</v>
+        <v>4.1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.36</v>
+        <v>12</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.36</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
         <v>11</v>
       </c>
-      <c r="BQ22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BZ22" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.23</v>
+        <v>5.3</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I23" t="n">
         <v>1.97</v>
@@ -6215,7 +6215,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O23" t="n">
         <v>1.28</v>
@@ -6230,7 +6230,7 @@
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6242,7 +6242,7 @@
         <v>2.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>2.72</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H24" t="n">
         <v>2.92</v>
@@ -6469,10 +6469,10 @@
         <v>1.14</v>
       </c>
       <c r="N24" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="O24" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="P24" t="n">
         <v>1.45</v>
@@ -6481,118 +6481,118 @@
         <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V24" t="n">
         <v>1.41</v>
       </c>
       <c r="W24" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
         <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
         <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
         <v>1.03</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G25" t="n">
         <v>2.04</v>
       </c>
       <c r="H25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
         <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6729,16 +6729,16 @@
         <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="T25" t="n">
         <v>1.69</v>
@@ -6747,118 +6747,118 @@
         <v>2.18</v>
       </c>
       <c r="V25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W25" t="n">
         <v>1.96</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL25" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.22</v>
+        <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.22</v>
+        <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.18</v>
+        <v>4.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.22</v>
+        <v>4.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.15</v>
+        <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.22</v>
+        <v>4.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.22</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.22</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.22</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.22</v>
+        <v>4.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.22</v>
+        <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.22</v>
+        <v>16.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.19</v>
+        <v>4.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.22</v>
+        <v>4.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.22</v>
+        <v>9</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.22</v>
+        <v>4.6</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         <v>4.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K26" t="n">
         <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
@@ -7001,7 +7001,7 @@
         <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W26" t="n">
         <v>2.08</v>
@@ -7010,19 +7010,19 @@
         <v>25</v>
       </c>
       <c r="Y26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z26" t="n">
         <v>42</v>
       </c>
       <c r="AA26" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB26" t="n">
         <v>13.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD26" t="n">
         <v>21</v>
@@ -7031,7 +7031,7 @@
         <v>60</v>
       </c>
       <c r="AF26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
@@ -7040,7 +7040,7 @@
         <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -7058,7 +7058,7 @@
         <v>12</v>
       </c>
       <c r="AO26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP26" t="n">
         <v>17</v>
@@ -7067,10 +7067,10 @@
         <v>16</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT26" t="n">
         <v>9.6</v>
@@ -7103,70 +7103,70 @@
         <v>15.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF26" t="n">
         <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="BJ26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP26" t="n">
         <v>13</v>
       </c>
-      <c r="BK26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>18</v>
-      </c>
       <c r="BQ26" t="n">
-        <v>1.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR26" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV26" t="n">
         <v>34</v>
       </c>
-      <c r="BS26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>46</v>
-      </c>
       <c r="BW26" t="n">
-        <v>1.86</v>
+        <v>7.6</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.87</v>
+        <v>8</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="O27" t="n">
         <v>1.36</v>
@@ -7246,7 +7246,7 @@
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G28" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="H28" t="n">
         <v>3.3</v>
@@ -7473,49 +7473,49 @@
         <v>3.85</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="U28" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
         <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y28" t="n">
         <v>970</v>
@@ -7524,19 +7524,19 @@
         <v>32</v>
       </c>
       <c r="AA28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF28" t="n">
         <v>970</v>
@@ -7548,67 +7548,67 @@
         <v>970</v>
       </c>
       <c r="AI28" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO28" t="n">
         <v>32</v>
       </c>
-      <c r="AK28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>38</v>
-      </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AQ28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
         <v>12</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA28" t="n">
         <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
         <v>1.01</v>
@@ -7617,16 +7617,16 @@
         <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BG28" t="n">
         <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
@@ -7638,43 +7638,43 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="BN28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>2.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>2.66</v>
+        <v>8.4</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>2.72</v>
       </c>
       <c r="G29" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="H29" t="n">
         <v>2.24</v>
@@ -7748,13 +7748,13 @@
         <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R29" t="n">
         <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T29" t="n">
         <v>1.6</v>
@@ -7766,7 +7766,7 @@
         <v>1.56</v>
       </c>
       <c r="W29" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X29" t="n">
         <v>21</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7969,230 +7969,230 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="G30" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="H30" t="n">
         <v>3.95</v>
       </c>
       <c r="I30" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.66</v>
+        <v>5.6</v>
       </c>
       <c r="O30" t="n">
         <v>1.1</v>
       </c>
       <c r="P30" t="n">
-        <v>1.29</v>
+        <v>2.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="S30" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="T30" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="U30" t="n">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI30" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK30" t="n">
         <v>1.01</v>
       </c>
       <c r="BL30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM30" t="n">
         <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO30" t="n">
         <v>1.01</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ30" t="n">
         <v>1.01</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS30" t="n">
         <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU30" t="n">
         <v>1.01</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW30" t="n">
         <v>1.01</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY30" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA30" t="n">
         <v>1.01</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>2.3</v>
       </c>
       <c r="I31" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J31" t="n">
         <v>3.15</v>
@@ -8241,13 +8241,13 @@
         <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="O31" t="n">
         <v>1.25</v>
@@ -8262,7 +8262,7 @@
         <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
         <v>1.61</v>
@@ -8271,7 +8271,7 @@
         <v>2.16</v>
       </c>
       <c r="V31" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W31" t="n">
         <v>1.41</v>
@@ -8280,7 +8280,7 @@
         <v>970</v>
       </c>
       <c r="Y31" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z31" t="n">
         <v>21</v>
@@ -8289,7 +8289,7 @@
         <v>42</v>
       </c>
       <c r="AB31" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AC31" t="n">
         <v>9.800000000000001</v>
@@ -8385,68 +8385,68 @@
         <v>4.1</v>
       </c>
       <c r="BH31" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="BJ31" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.94</v>
+        <v>6.4</v>
       </c>
       <c r="BN31" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.82</v>
+        <v>5.3</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.86</v>
+        <v>5.7</v>
       </c>
       <c r="BT31" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.55</v>
+        <v>3.25</v>
       </c>
       <c r="BV31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.85</v>
+        <v>5.6</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.83</v>
+        <v>5.4</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8501,13 +8501,13 @@
         <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O32" t="n">
         <v>1.24</v>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
         <v>1.66</v>
@@ -8531,7 +8531,7 @@
         <v>1.5</v>
       </c>
       <c r="X32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="n">
         <v>14.5</v>
@@ -8546,10 +8546,10 @@
         <v>15.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE32" t="n">
         <v>27</v>
@@ -8585,58 +8585,58 @@
         <v>18</v>
       </c>
       <c r="AP32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ32" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AR32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY32" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AZ32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF32" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC32" t="n">
+      <c r="BG32" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>4.9</v>
       </c>
       <c r="BH32" t="n">
         <v>4.2</v>
@@ -8678,7 +8678,7 @@
         <v>6.2</v>
       </c>
       <c r="BU32" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BV32" t="n">
         <v>19</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G33" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H33" t="n">
         <v>5.1</v>
@@ -8743,19 +8743,19 @@
         <v>6.6</v>
       </c>
       <c r="J33" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K33" t="n">
         <v>5.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>1.17</v>
@@ -8770,25 +8770,25 @@
         <v>1.56</v>
       </c>
       <c r="S33" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="T33" t="n">
         <v>1.62</v>
       </c>
       <c r="U33" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
         <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="X33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z33" t="n">
         <v>60</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8985,13 +8985,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I34" t="n">
         <v>5</v>
@@ -9003,7 +9003,7 @@
         <v>4.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M34" t="n">
         <v>1.03</v>
@@ -9036,7 +9036,7 @@
         <v>1.25</v>
       </c>
       <c r="W34" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X34" t="n">
         <v>32</v>
@@ -9051,10 +9051,10 @@
         <v>110</v>
       </c>
       <c r="AB34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD34" t="n">
         <v>23</v>
@@ -9090,7 +9090,7 @@
         <v>8</v>
       </c>
       <c r="AO34" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP34" t="n">
         <v>19</v>
@@ -9195,7 +9195,7 @@
         <v>7.4</v>
       </c>
       <c r="BX34" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
         <v>7.4</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
         <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R35" t="n">
         <v>1.96</v>
@@ -9395,7 +9395,7 @@
         <v>4</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG35" t="n">
         <v>10</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -9747,16 +9747,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="G37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H37" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="I37" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="J37" t="n">
         <v>4.2</v>
@@ -9765,7 +9765,7 @@
         <v>4.8</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
         <v>1.02</v>
@@ -9777,31 +9777,31 @@
         <v>1.14</v>
       </c>
       <c r="P37" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R37" t="n">
         <v>1.79</v>
       </c>
       <c r="S37" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T37" t="n">
         <v>1.45</v>
       </c>
       <c r="U37" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V37" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="W37" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X37" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Y37" t="n">
         <v>21</v>
@@ -9828,7 +9828,7 @@
         <v>44</v>
       </c>
       <c r="AG37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH37" t="n">
         <v>19</v>
@@ -9837,22 +9837,22 @@
         <v>28</v>
       </c>
       <c r="AJ37" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AK37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM37" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO37" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP37" t="n">
         <v>1.03</v>
@@ -9864,7 +9864,7 @@
         <v>12.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AT37" t="n">
         <v>1.01</v>
@@ -9903,19 +9903,19 @@
         <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG37" t="n">
         <v>6</v>
       </c>
       <c r="BH37" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.06</v>
+        <v>4.5</v>
       </c>
       <c r="BJ37" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BK37" t="n">
         <v>5.3</v>
@@ -9924,43 +9924,43 @@
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>2.78</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN37" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BO37" t="n">
         <v>4.9</v>
       </c>
       <c r="BP37" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ37" t="n">
-        <v>2.64</v>
+        <v>7.8</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>2.66</v>
+        <v>8</v>
       </c>
       <c r="BT37" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU37" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV37" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="BX37" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>2.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -10004,16 +10004,16 @@
         <v>1.81</v>
       </c>
       <c r="G38" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H38" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I38" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K38" t="n">
         <v>5</v>
@@ -10025,7 +10025,7 @@
         <v>1.02</v>
       </c>
       <c r="N38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O38" t="n">
         <v>1.14</v>
@@ -10034,25 +10034,25 @@
         <v>2.86</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="R38" t="n">
         <v>1.76</v>
       </c>
       <c r="S38" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T38" t="n">
         <v>1.49</v>
       </c>
       <c r="U38" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W38" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X38" t="n">
         <v>38</v>
@@ -10061,37 +10061,37 @@
         <v>30</v>
       </c>
       <c r="Z38" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA38" t="n">
         <v>85</v>
       </c>
       <c r="AB38" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC38" t="n">
         <v>13.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE38" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF38" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG38" t="n">
         <v>13</v>
       </c>
       <c r="AH38" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI38" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK38" t="n">
         <v>19.5</v>
@@ -10103,7 +10103,7 @@
         <v>60</v>
       </c>
       <c r="AN38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO38" t="n">
         <v>28</v>
@@ -10112,7 +10112,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ38" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR38" t="n">
         <v>1.01</v>
@@ -10121,7 +10121,7 @@
         <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU38" t="n">
         <v>9</v>
@@ -10133,22 +10133,22 @@
         <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY38" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA38" t="n">
         <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD38" t="n">
         <v>18</v>
@@ -10157,10 +10157,10 @@
         <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG38" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
         <v>6.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="M39" t="n">
         <v>1.01</v>
@@ -10288,7 +10288,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R39" t="n">
         <v>1.84</v>
@@ -10417,16 +10417,16 @@
         <v>3.9</v>
       </c>
       <c r="BH39" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.1</v>
+        <v>3.65</v>
       </c>
       <c r="BJ39" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.81</v>
+        <v>4.9</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
@@ -10435,40 +10435,40 @@
         <v>2.06</v>
       </c>
       <c r="BN39" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="BP39" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.85</v>
+        <v>5.3</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.95</v>
+        <v>6.8</v>
       </c>
       <c r="BT39" t="n">
         <v>13</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.82</v>
+        <v>5</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="BZ39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>3.1</v>
       </c>
       <c r="J40" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K40" t="n">
         <v>3.85</v>
@@ -10542,13 +10542,13 @@
         <v>2.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R40" t="n">
         <v>1.46</v>
       </c>
       <c r="S40" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T40" t="n">
         <v>1.65</v>
@@ -10572,7 +10572,7 @@
         <v>26</v>
       </c>
       <c r="AA40" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB40" t="n">
         <v>14.5</v>
@@ -10593,7 +10593,7 @@
         <v>13.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI40" t="n">
         <v>44</v>
@@ -10611,10 +10611,10 @@
         <v>85</v>
       </c>
       <c r="AN40" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP40" t="n">
         <v>16</v>
@@ -10626,7 +10626,7 @@
         <v>19.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT40" t="n">
         <v>11</v>
@@ -10638,7 +10638,7 @@
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX40" t="n">
         <v>15</v>
@@ -10650,22 +10650,22 @@
         <v>14</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BC40" t="n">
         <v>21</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE40" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG40" t="n">
         <v>18.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
         <v>1.37</v>
       </c>
       <c r="J41" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K41" t="n">
         <v>6.2</v>
@@ -10796,7 +10796,7 @@
         <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R41" t="n">
         <v>1.55</v>
@@ -10817,19 +10817,19 @@
         <v>1.09</v>
       </c>
       <c r="X41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y41" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z41" t="n">
         <v>10.5</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>8.4</v>
       </c>
       <c r="AA41" t="n">
         <v>11</v>
       </c>
       <c r="AB41" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC41" t="n">
         <v>14</v>
@@ -10838,22 +10838,22 @@
         <v>11</v>
       </c>
       <c r="AE41" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AF41" t="n">
         <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AH41" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AI41" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ41" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="AK41" t="n">
         <v>1000</v>
@@ -10907,19 +10907,19 @@
         <v>23</v>
       </c>
       <c r="BB41" t="n">
-        <v>90</v>
+        <v>8.4</v>
       </c>
       <c r="BC41" t="n">
-        <v>44</v>
+        <v>8.6</v>
       </c>
       <c r="BD41" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="BF41" t="n">
-        <v>48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG41" t="n">
         <v>4.7</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -11017,61 +11017,61 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G42" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="H42" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I42" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J42" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="K42" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L42" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
         <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="O42" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P42" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T42" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U42" t="n">
         <v>1.98</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W42" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="X42" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y42" t="n">
         <v>11.5</v>
@@ -11083,10 +11083,10 @@
         <v>75</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC42" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42" t="n">
         <v>17.5</v>
@@ -11122,70 +11122,70 @@
         <v>34</v>
       </c>
       <c r="AO42" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW42" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AX42" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY42" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB42" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ42" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK42" t="n">
         <v>1.01</v>
@@ -11197,13 +11197,13 @@
         <v>1.01</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO42" t="n">
         <v>1.01</v>
       </c>
       <c r="BP42" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ42" t="n">
         <v>1.01</v>
@@ -11215,7 +11215,7 @@
         <v>1.01</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -11274,19 +11274,19 @@
         <v>1.87</v>
       </c>
       <c r="G43" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H43" t="n">
         <v>4.9</v>
       </c>
       <c r="I43" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J43" t="n">
         <v>3.45</v>
       </c>
       <c r="K43" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L43" t="n">
         <v>1.44</v>
@@ -11295,28 +11295,28 @@
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O43" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P43" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R43" t="n">
         <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T43" t="n">
         <v>2.08</v>
       </c>
       <c r="U43" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V43" t="n">
         <v>1.23</v>
@@ -11331,10 +11331,10 @@
         <v>16</v>
       </c>
       <c r="Z43" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA43" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB43" t="n">
         <v>7.8</v>
@@ -11343,7 +11343,7 @@
         <v>9</v>
       </c>
       <c r="AD43" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE43" t="n">
         <v>100</v>
@@ -11355,7 +11355,7 @@
         <v>12.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI43" t="n">
         <v>110</v>
@@ -11370,13 +11370,13 @@
         <v>60</v>
       </c>
       <c r="AM43" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN43" t="n">
         <v>19</v>
       </c>
       <c r="AO43" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP43" t="n">
         <v>9.4</v>
@@ -11388,7 +11388,7 @@
         <v>32</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT43" t="n">
         <v>6.2</v>
@@ -11400,7 +11400,7 @@
         <v>18</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX43" t="n">
         <v>9.4</v>
@@ -11412,7 +11412,7 @@
         <v>20</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB43" t="n">
         <v>19.5</v>
@@ -11421,25 +11421,25 @@
         <v>21</v>
       </c>
       <c r="BD43" t="n">
-        <v>42</v>
+        <v>5.8</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF43" t="n">
         <v>14.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH43" t="n">
         <v>2.96</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BJ43" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK43" t="n">
         <v>6.8</v>
@@ -11448,7 +11448,7 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BN43" t="n">
         <v>4.4</v>
@@ -11460,41 +11460,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ43" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR43" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT43" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU43" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX43" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY43" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BZ43" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
         <v>2.48</v>
       </c>
       <c r="I44" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J44" t="n">
         <v>3.9</v>
@@ -11558,10 +11558,10 @@
         <v>2.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="R44" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S44" t="n">
         <v>2.24</v>
@@ -11573,7 +11573,7 @@
         <v>2.68</v>
       </c>
       <c r="V44" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W44" t="n">
         <v>1.54</v>
@@ -11585,7 +11585,7 @@
         <v>970</v>
       </c>
       <c r="Z44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA44" t="n">
         <v>42</v>
@@ -11600,7 +11600,7 @@
         <v>15</v>
       </c>
       <c r="AE44" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF44" t="n">
         <v>26</v>
@@ -11630,7 +11630,7 @@
         <v>15</v>
       </c>
       <c r="AO44" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP44" t="n">
         <v>21</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -12057,13 +12057,13 @@
         <v>1.02</v>
       </c>
       <c r="N46" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O46" t="n">
         <v>1.11</v>
       </c>
       <c r="P46" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q46" t="n">
         <v>1.35</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="G47" t="n">
         <v>1000</v>
@@ -12311,22 +12311,22 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O47" t="n">
         <v>1.02</v>
       </c>
       <c r="P47" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="R47" t="n">
         <v>1.07</v>
       </c>
       <c r="S47" t="n">
-        <v>2.8</v>
+        <v>1.05</v>
       </c>
       <c r="T47" t="n">
         <v>1.11</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -12571,22 +12571,22 @@
         <v>1.32</v>
       </c>
       <c r="P48" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R48" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S48" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T48" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U48" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V48" t="n">
         <v>1.85</v>
@@ -12619,7 +12619,7 @@
         <v>24</v>
       </c>
       <c r="AF48" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AG48" t="n">
         <v>17</v>
@@ -12634,16 +12634,16 @@
         <v>85</v>
       </c>
       <c r="AK48" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL48" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM48" t="n">
         <v>120</v>
       </c>
       <c r="AN48" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO48" t="n">
         <v>17.5</v>
@@ -12673,7 +12673,7 @@
         <v>19.5</v>
       </c>
       <c r="AX48" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY48" t="n">
         <v>13.5</v>
@@ -12682,19 +12682,19 @@
         <v>15.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB48" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC48" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC48" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD48" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF48" t="n">
         <v>40</v>
@@ -12703,58 +12703,58 @@
         <v>12.5</v>
       </c>
       <c r="BH48" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ48" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN48" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BP48" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR48" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT48" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV48" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX48" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ48" t="n">
         <v>0</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="G49" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H49" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I49" t="n">
         <v>2.14</v>
@@ -12810,34 +12810,34 @@
         <v>3.05</v>
       </c>
       <c r="K49" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M49" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N49" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O49" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P49" t="n">
         <v>1.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R49" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S49" t="n">
         <v>4.8</v>
       </c>
       <c r="T49" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U49" t="n">
         <v>1.71</v>
@@ -12846,10 +12846,10 @@
         <v>1.87</v>
       </c>
       <c r="W49" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X49" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y49" t="n">
         <v>7</v>
@@ -12897,118 +12897,118 @@
         <v>230</v>
       </c>
       <c r="AN49" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AO49" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AR49" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AS49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX49" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT49" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>5</v>
-      </c>
       <c r="AY49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>4.6</v>
       </c>
-      <c r="AZ49" t="n">
+      <c r="BA49" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG49" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA49" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG49" t="n">
+      <c r="BH49" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT49" t="n">
         <v>4.6</v>
       </c>
-      <c r="BH49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI49" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BP49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BR49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BT49" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU49" t="n">
-        <v>1.46</v>
+        <v>3.15</v>
       </c>
       <c r="BV49" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.46</v>
+        <v>6.4</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="BZ49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G50" t="n">
         <v>1.74</v>
@@ -13067,7 +13067,7 @@
         <v>5.3</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M50" t="n">
         <v>1.02</v>
@@ -13151,118 +13151,118 @@
         <v>65</v>
       </c>
       <c r="AN50" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AO50" t="n">
         <v>34</v>
       </c>
       <c r="AP50" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ50" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR50" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS50" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AT50" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AU50" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AV50" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX50" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY50" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ50" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB50" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BC50" t="n">
         <v>11</v>
       </c>
       <c r="BD50" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE50" t="n">
-        <v>38</v>
+        <v>5.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>90</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BS50" t="n">
         <v>7.6</v>
       </c>
-      <c r="BI50" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ50" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK50" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BN50" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP50" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ50" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BR50" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS50" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BT50" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU50" t="n">
-        <v>2.36</v>
+        <v>5.8</v>
       </c>
       <c r="BV50" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BW50" t="n">
-        <v>2.72</v>
+        <v>9.6</v>
       </c>
       <c r="BX50" t="n">
         <v>46</v>
       </c>
       <c r="BY50" t="n">
-        <v>2.72</v>
+        <v>9.4</v>
       </c>
       <c r="BZ50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -13318,49 +13318,49 @@
         <v>3.45</v>
       </c>
       <c r="K51" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L51" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="M51" t="n">
         <v>1.06</v>
       </c>
       <c r="N51" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O51" t="n">
         <v>1.31</v>
       </c>
       <c r="P51" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R51" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T51" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U51" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V51" t="n">
         <v>1.51</v>
       </c>
       <c r="W51" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X51" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z51" t="n">
         <v>21</v>
@@ -13369,7 +13369,7 @@
         <v>55</v>
       </c>
       <c r="AB51" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC51" t="n">
         <v>8.199999999999999</v>
@@ -13405,13 +13405,13 @@
         <v>100</v>
       </c>
       <c r="AN51" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO51" t="n">
         <v>28</v>
       </c>
-      <c r="AO51" t="n">
-        <v>34</v>
-      </c>
       <c r="AP51" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ51" t="n">
         <v>10.5</v>
@@ -13420,10 +13420,10 @@
         <v>16.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT51" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU51" t="n">
         <v>7</v>
@@ -13432,7 +13432,7 @@
         <v>11</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX51" t="n">
         <v>15.5</v>
@@ -13441,22 +13441,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE51" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF51" t="n">
         <v>16.5</v>
@@ -13465,58 +13465,58 @@
         <v>18</v>
       </c>
       <c r="BH51" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="BJ51" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.63</v>
+        <v>5.8</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.86</v>
+        <v>9.6</v>
       </c>
       <c r="BN51" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS51" t="n">
         <v>8</v>
       </c>
-      <c r="BO51" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP51" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BR51" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS51" t="n">
-        <v>1.79</v>
-      </c>
       <c r="BT51" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BU51" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV51" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.75</v>
+        <v>7.2</v>
       </c>
       <c r="BX51" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.79</v>
+        <v>8</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G52" t="n">
         <v>2.38</v>
@@ -13566,13 +13566,13 @@
         <v>1.73</v>
       </c>
       <c r="I52" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J52" t="n">
-        <v>1.75</v>
+        <v>1.09</v>
       </c>
       <c r="K52" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -13811,25 +13811,25 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G53" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H53" t="n">
         <v>3.3</v>
       </c>
       <c r="I53" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J53" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K53" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L53" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M53" t="n">
         <v>1.06</v>
@@ -13838,46 +13838,46 @@
         <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P53" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R53" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S53" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T53" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U53" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V53" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W53" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X53" t="n">
         <v>17.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA53" t="n">
         <v>70</v>
       </c>
       <c r="AB53" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC53" t="n">
         <v>10</v>
@@ -13886,13 +13886,13 @@
         <v>17.5</v>
       </c>
       <c r="AE53" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF53" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG53" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH53" t="n">
         <v>20</v>
@@ -13901,19 +13901,19 @@
         <v>60</v>
       </c>
       <c r="AJ53" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AK53" t="n">
         <v>25</v>
       </c>
       <c r="AL53" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM53" t="n">
         <v>100</v>
       </c>
       <c r="AN53" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO53" t="n">
         <v>36</v>
@@ -13928,103 +13928,103 @@
         <v>21</v>
       </c>
       <c r="AS53" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AT53" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU53" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV53" t="n">
         <v>12.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX53" t="n">
         <v>12.5</v>
       </c>
       <c r="AY53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ53" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BB53" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC53" t="n">
         <v>19.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF53" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG53" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH53" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.85</v>
+        <v>2.86</v>
       </c>
       <c r="BJ53" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.85</v>
+        <v>9.6</v>
       </c>
       <c r="BN53" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BO53" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BP53" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.72</v>
+        <v>6.4</v>
       </c>
       <c r="BR53" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.77</v>
+        <v>7.8</v>
       </c>
       <c r="BT53" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BU53" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV53" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX53" t="n">
         <v>38</v>
       </c>
-      <c r="BW53" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BX53" t="n">
-        <v>50</v>
-      </c>
       <c r="BY53" t="n">
-        <v>1.79</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -14065,22 +14065,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G54" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H54" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I54" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K54" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14089,46 +14089,46 @@
         <v>1.07</v>
       </c>
       <c r="N54" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O54" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P54" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R54" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
         <v>3.3</v>
       </c>
       <c r="T54" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U54" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V54" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W54" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X54" t="n">
         <v>16</v>
       </c>
       <c r="Y54" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA54" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB54" t="n">
         <v>10</v>
@@ -14143,7 +14143,7 @@
         <v>50</v>
       </c>
       <c r="AF54" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG54" t="n">
         <v>11</v>
@@ -14152,7 +14152,7 @@
         <v>19</v>
       </c>
       <c r="AI54" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ54" t="n">
         <v>26</v>
@@ -14170,7 +14170,7 @@
         <v>16</v>
       </c>
       <c r="AO54" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP54" t="n">
         <v>13</v>
@@ -14179,10 +14179,10 @@
         <v>12.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS54" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT54" t="n">
         <v>8.6</v>
@@ -14194,7 +14194,7 @@
         <v>13.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AX54" t="n">
         <v>11</v>
@@ -14206,7 +14206,7 @@
         <v>15.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB54" t="n">
         <v>21</v>
@@ -14215,70 +14215,70 @@
         <v>18.5</v>
       </c>
       <c r="BD54" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE54" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF54" t="n">
         <v>12.5</v>
       </c>
       <c r="BG54" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BJ54" t="n">
         <v>13</v>
       </c>
       <c r="BK54" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BN54" t="n">
         <v>6.4</v>
       </c>
       <c r="BO54" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP54" t="n">
         <v>20</v>
       </c>
       <c r="BQ54" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BR54" t="n">
         <v>38</v>
       </c>
       <c r="BS54" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BT54" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU54" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV54" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW54" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BZ54" t="n">
         <v>0</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -14322,19 +14322,19 @@
         <v>2.28</v>
       </c>
       <c r="G55" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H55" t="n">
         <v>2.66</v>
       </c>
       <c r="I55" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>3.9</v>
       </c>
       <c r="K55" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L55" t="n">
         <v>1.2</v>
@@ -14343,34 +14343,34 @@
         <v>1.02</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="O55" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P55" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R55" t="n">
         <v>1.77</v>
       </c>
       <c r="S55" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T55" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="U55" t="n">
-        <v>1.11</v>
+        <v>2.84</v>
       </c>
       <c r="V55" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X55" t="n">
         <v>42</v>
@@ -14388,7 +14388,7 @@
         <v>24</v>
       </c>
       <c r="AC55" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD55" t="n">
         <v>17</v>
@@ -14409,7 +14409,7 @@
         <v>34</v>
       </c>
       <c r="AJ55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK55" t="n">
         <v>26</v>
@@ -14430,7 +14430,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ55" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR55" t="n">
         <v>18.5</v>
@@ -14442,7 +14442,7 @@
         <v>14</v>
       </c>
       <c r="AU55" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV55" t="n">
         <v>10</v>
@@ -14469,13 +14469,13 @@
         <v>15.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE55" t="n">
         <v>1.01</v>
       </c>
       <c r="BF55" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG55" t="n">
         <v>9.6</v>
@@ -14496,7 +14496,7 @@
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN55" t="n">
         <v>6.4</v>
@@ -14514,35 +14514,35 @@
         <v>22</v>
       </c>
       <c r="BS55" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT55" t="n">
         <v>7</v>
       </c>
       <c r="BU55" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV55" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="BW55" t="n">
         <v>6.8</v>
       </c>
       <c r="BX55" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ55" t="n">
         <v>13</v>
       </c>
       <c r="CA55" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -14573,16 +14573,16 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G56" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H56" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="I56" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J56" t="n">
         <v>3.7</v>
@@ -14603,28 +14603,28 @@
         <v>1.33</v>
       </c>
       <c r="P56" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q56" t="n">
         <v>1.98</v>
       </c>
       <c r="R56" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S56" t="n">
         <v>3.55</v>
       </c>
       <c r="T56" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U56" t="n">
         <v>1.92</v>
       </c>
       <c r="V56" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W56" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X56" t="n">
         <v>16.5</v>
@@ -14636,10 +14636,10 @@
         <v>13</v>
       </c>
       <c r="AA56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC56" t="n">
         <v>10.5</v>
@@ -14651,49 +14651,49 @@
         <v>25</v>
       </c>
       <c r="AF56" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AG56" t="n">
         <v>25</v>
       </c>
       <c r="AH56" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI56" t="n">
         <v>48</v>
       </c>
       <c r="AJ56" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK56" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AL56" t="n">
         <v>95</v>
       </c>
       <c r="AM56" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN56" t="n">
         <v>120</v>
       </c>
       <c r="AO56" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP56" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ56" t="n">
         <v>7</v>
       </c>
       <c r="AR56" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS56" t="n">
         <v>16</v>
       </c>
       <c r="AT56" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU56" t="n">
         <v>7.4</v>
@@ -14702,7 +14702,7 @@
         <v>8.6</v>
       </c>
       <c r="AW56" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="AX56" t="n">
         <v>3.95</v>
@@ -14732,61 +14732,61 @@
         <v>4.1</v>
       </c>
       <c r="BG56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH56" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK56" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN56" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP56" t="n">
         <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT56" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV56" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ56" t="n">
         <v>0</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G57" t="n">
         <v>1.84</v>
@@ -14842,7 +14842,7 @@
         <v>3.5</v>
       </c>
       <c r="K57" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L57" t="n">
         <v>1.45</v>
@@ -14854,7 +14854,7 @@
         <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P57" t="n">
         <v>1.68</v>
@@ -14878,7 +14878,7 @@
         <v>1.2</v>
       </c>
       <c r="W57" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X57" t="n">
         <v>13</v>
@@ -14890,10 +14890,10 @@
         <v>60</v>
       </c>
       <c r="AA57" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB57" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC57" t="n">
         <v>8.4</v>
@@ -14935,58 +14935,58 @@
         <v>230</v>
       </c>
       <c r="AP57" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ57" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR57" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS57" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT57" t="n">
         <v>6.2</v>
       </c>
       <c r="AU57" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV57" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW57" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX57" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY57" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ57" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA57" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB57" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC57" t="n">
         <v>6</v>
       </c>
       <c r="BD57" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE57" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF57" t="n">
         <v>10.5</v>
       </c>
       <c r="BG57" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -15243,68 +15243,68 @@
         <v>4.3</v>
       </c>
       <c r="BH58" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI58" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BJ58" t="n">
         <v>1000</v>
       </c>
       <c r="BK58" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BL58" t="n">
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN58" t="n">
         <v>1000</v>
       </c>
       <c r="BO58" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP58" t="n">
         <v>1000</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BR58" t="n">
         <v>1000</v>
       </c>
       <c r="BS58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BT58" t="n">
         <v>1000</v>
       </c>
       <c r="BU58" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BV58" t="n">
         <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BX58" t="n">
         <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ58" t="n">
         <v>1000</v>
       </c>
       <c r="CA58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -15335,13 +15335,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="G59" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="H59" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="I59" t="n">
         <v>3.25</v>
@@ -15350,205 +15350,205 @@
         <v>2.56</v>
       </c>
       <c r="K59" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="L59" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M59" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N59" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="O59" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="P59" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="Q59" t="n">
         <v>2.52</v>
       </c>
       <c r="R59" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S59" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X59" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU59" t="n">
         <v>2.92</v>
       </c>
-      <c r="T59" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AV59" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH59" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI59" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ59" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK59" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BN59" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO59" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP59" t="n">
         <v>1000</v>
       </c>
       <c r="BQ59" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BR59" t="n">
         <v>1000</v>
       </c>
       <c r="BS59" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BT59" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU59" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV59" t="n">
         <v>1000</v>
       </c>
       <c r="BW59" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BX59" t="n">
         <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BZ59" t="n">
         <v>0</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
         <v>1.66</v>
       </c>
       <c r="O62" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="P62" t="n">
         <v>1.66</v>
@@ -16136,7 +16136,7 @@
         <v>1.16</v>
       </c>
       <c r="S62" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="T62" t="n">
         <v>1.01</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -16390,7 +16390,7 @@
         <v>1.16</v>
       </c>
       <c r="S63" t="n">
-        <v>1.32</v>
+        <v>2.36</v>
       </c>
       <c r="T63" t="n">
         <v>1.11</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -16767,68 +16767,68 @@
         <v>4.3</v>
       </c>
       <c r="BH64" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI64" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN64" t="n">
         <v>1000</v>
       </c>
       <c r="BO64" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP64" t="n">
         <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BT64" t="n">
         <v>1000</v>
       </c>
       <c r="BU64" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV64" t="n">
         <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BX64" t="n">
         <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BZ64" t="n">
         <v>1000</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="I2" t="n">
         <v>2.5</v>
@@ -872,22 +872,22 @@
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
         <v>2.04</v>
@@ -896,25 +896,25 @@
         <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
         <v>18.5</v>
@@ -923,37 +923,37 @@
         <v>38</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
         <v>30</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>440</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -962,82 +962,82 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP2" t="n">
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>29</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC2" t="n">
         <v>27</v>
       </c>
       <c r="BD2" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG2" t="n">
         <v>13.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.2</v>
+        <v>1.85</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO2" t="n">
         <v>5</v>
@@ -1046,16 +1046,16 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU2" t="n">
         <v>4.1</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="G3" t="n">
         <v>6.4</v>
@@ -1120,28 +1120,28 @@
         <v>1.81</v>
       </c>
       <c r="I3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
         <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
         <v>2.42</v>
@@ -1150,7 +1150,7 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
         <v>2.12</v>
@@ -1162,7 +1162,7 @@
         <v>2.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>13.5</v>
@@ -1222,13 +1222,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
         <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1240,13 +1240,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>18</v>
@@ -1255,64 +1255,64 @@
         <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
         <v>5</v>
       </c>
-      <c r="BE3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="BT3" t="n">
         <v>4.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H4" t="n">
         <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.5</v>
@@ -1398,7 +1398,7 @@
         <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1524,7 +1524,7 @@
         <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>2.78</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
         <v>3.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I5" t="n">
         <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1652,7 +1652,7 @@
         <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
@@ -1661,22 +1661,22 @@
         <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
         <v>1.86</v>
       </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.43</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>44</v>
@@ -1691,7 +1691,7 @@
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
         <v>230</v>
@@ -1700,7 +1700,7 @@
         <v>48</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>80</v>
@@ -1718,7 +1718,7 @@
         <v>450</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>600</v>
@@ -1736,55 +1736,55 @@
         <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
         <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="BF5" t="n">
         <v>7.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>1.61</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
         <v>8.4</v>
@@ -1894,13 +1894,13 @@
         <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
         <v>2.54</v>
@@ -1924,7 +1924,7 @@
         <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X6" t="n">
         <v>50</v>
@@ -1996,7 +1996,7 @@
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>18</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>5.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
@@ -2154,7 +2154,7 @@
         <v>5.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
         <v>2.44</v>
@@ -2172,7 +2172,7 @@
         <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
         <v>1.15</v>
@@ -2196,19 +2196,19 @@
         <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE7" t="n">
         <v>480</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>44</v>
@@ -2220,7 +2220,7 @@
         <v>36</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
         <v>75</v>
@@ -2265,19 +2265,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
         <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE7" t="n">
         <v>7.2</v>
@@ -2316,7 +2316,7 @@
         <v>9.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
@@ -2510,7 +2510,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2522,7 +2522,7 @@
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB8" t="n">
         <v>17.5</v>
@@ -2534,7 +2534,7 @@
         <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF8" t="n">
         <v>6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
         <v>2.74</v>
@@ -2647,10 +2647,10 @@
         <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.2</v>
@@ -2686,7 +2686,7 @@
         <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X9" t="n">
         <v>130</v>
@@ -2752,7 +2752,7 @@
         <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
@@ -2779,7 +2779,7 @@
         <v>15</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
         <v>10.5</v>
@@ -2794,7 +2794,7 @@
         <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -2925,22 +2925,22 @@
         <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U10" t="n">
         <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X10" t="n">
         <v>38</v>
@@ -2991,7 +2991,7 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>17.5</v>
       </c>
       <c r="AO10" t="n">
         <v>15.5</v>
@@ -3006,19 +3006,19 @@
         <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
         <v>15</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -3030,19 +3030,19 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB10" t="n">
         <v>16</v>
       </c>
-      <c r="BB10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10" t="n">
         <v>14.5</v>
@@ -3054,7 +3054,7 @@
         <v>4.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10" t="n">
         <v>9</v>
@@ -3072,13 +3072,13 @@
         <v>6.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP10" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
         <v>26</v>
@@ -3090,7 +3090,7 @@
         <v>6.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
         <v>19.5</v>
@@ -3108,11 +3108,11 @@
         <v>17.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>2.46</v>
       </c>
       <c r="H11" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
         <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>1.26</v>
@@ -3167,40 +3167,40 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U11" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V11" t="n">
         <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z11" t="n">
         <v>24</v>
@@ -3209,16 +3209,16 @@
         <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF11" t="n">
         <v>19</v>
@@ -3227,31 +3227,31 @@
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ11" t="n">
         <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
         <v>38</v>
       </c>
       <c r="AM11" t="n">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ11" t="n">
         <v>15.5</v>
@@ -3263,7 +3263,7 @@
         <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU11" t="n">
         <v>8.6</v>
@@ -3287,7 +3287,7 @@
         <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
@@ -3296,13 +3296,13 @@
         <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BF11" t="n">
         <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH11" t="n">
         <v>4.3</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
         <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S12" t="n">
         <v>2.22</v>
@@ -3466,7 +3466,7 @@
         <v>24</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
@@ -3541,22 +3541,22 @@
         <v>18.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
         <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="n">
         <v>5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H13" t="n">
         <v>2.96</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>1.36</v>
@@ -3678,7 +3678,7 @@
         <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
         <v>1.8</v>
@@ -3693,13 +3693,13 @@
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
         <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
         <v>1.58</v>
@@ -3711,19 +3711,19 @@
         <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
         <v>9</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>44</v>
@@ -3750,13 +3750,13 @@
         <v>46</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN13" t="n">
         <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
         <v>7</v>
@@ -3768,7 +3768,7 @@
         <v>4.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>8.199999999999999</v>
@@ -3777,13 +3777,13 @@
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
         <v>9</v>
@@ -3792,7 +3792,7 @@
         <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
@@ -3801,7 +3801,7 @@
         <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>24</v>
+        <v>5.8</v>
       </c>
       <c r="BE13" t="n">
         <v>5.4</v>
@@ -3810,71 +3810,71 @@
         <v>16</v>
       </c>
       <c r="BG13" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13" t="n">
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO13" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="BP13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR13" t="n">
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BT13" t="n">
         <v>7.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="BV13" t="n">
         <v>29</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BX13" t="n">
         <v>42</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -3917,10 +3917,10 @@
         <v>2.06</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.21</v>
@@ -3938,7 +3938,7 @@
         <v>2.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R14" t="n">
         <v>1.81</v>
@@ -4037,7 +4037,7 @@
         <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
         <v>8.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H15" t="n">
         <v>2.78</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
         <v>4.4</v>
@@ -4207,7 +4207,7 @@
         <v>2.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
         <v>1.66</v>
@@ -4330,13 +4330,13 @@
         <v>8.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN15" t="n">
         <v>6.2</v>
@@ -4348,13 +4348,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR15" t="n">
         <v>23</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT15" t="n">
         <v>7</v>
@@ -4366,23 +4366,23 @@
         <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX15" t="n">
         <v>26</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>14.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I16" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.54</v>
@@ -4437,16 +4437,16 @@
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
@@ -4461,19 +4461,19 @@
         <v>1.86</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
         <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y16" t="n">
         <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
         <v>130</v>
@@ -4491,10 +4491,10 @@
         <v>110</v>
       </c>
       <c r="AF16" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>30</v>
@@ -4557,16 +4557,16 @@
         <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC16" t="n">
         <v>26</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
         <v>32</v>
@@ -4575,10 +4575,10 @@
         <v>24</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4590,10 +4590,10 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO16" t="n">
         <v>4.5</v>
@@ -4602,16 +4602,16 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU16" t="n">
         <v>4.2</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K17" t="n">
         <v>4.8</v>
@@ -4700,7 +4700,7 @@
         <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
@@ -4709,16 +4709,16 @@
         <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
         <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="X17" t="n">
         <v>16.5</v>
@@ -4733,10 +4733,10 @@
         <v>320</v>
       </c>
       <c r="AB17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
         <v>32</v>
@@ -4745,7 +4745,7 @@
         <v>190</v>
       </c>
       <c r="AF17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG17" t="n">
         <v>10.5</v>
@@ -4757,10 +4757,10 @@
         <v>470</v>
       </c>
       <c r="AJ17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL17" t="n">
         <v>42</v>
@@ -4772,61 +4772,61 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO17" t="n">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AP17" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY17" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC17" t="n">
         <v>14</v>
       </c>
       <c r="BD17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
         <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH17" t="n">
         <v>3.65</v>
@@ -4838,13 +4838,13 @@
         <v>12</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
         <v>4.1</v>
@@ -4853,7 +4853,7 @@
         <v>3.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ17" t="n">
         <v>5.1</v>
@@ -4862,35 +4862,35 @@
         <v>28</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT17" t="n">
         <v>11.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>19.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H18" t="n">
         <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -4948,7 +4948,7 @@
         <v>2.76</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P18" t="n">
         <v>1.6</v>
@@ -4963,16 +4963,16 @@
         <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V18" t="n">
         <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X18" t="n">
         <v>18.5</v>
@@ -4984,10 +4984,10 @@
         <v>970</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC18" t="n">
         <v>7.6</v>
@@ -4996,31 +4996,31 @@
         <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
         <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AK18" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
         <v>600</v>
@@ -5029,58 +5029,58 @@
         <v>600</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BH18" t="n">
         <v>2.98</v>
@@ -5104,7 +5104,7 @@
         <v>6</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
         <v>4.6</v>
@@ -5193,7 +5193,7 @@
         <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -5205,7 +5205,7 @@
         <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
         <v>1.98</v>
@@ -5217,7 +5217,7 @@
         <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
         <v>2.02</v>
@@ -5229,7 +5229,7 @@
         <v>1.87</v>
       </c>
       <c r="X19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="n">
         <v>15.5</v>
@@ -5238,7 +5238,7 @@
         <v>100</v>
       </c>
       <c r="AA19" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
         <v>10.5</v>
@@ -5253,10 +5253,10 @@
         <v>370</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
         <v>19.5</v>
@@ -5277,70 +5277,70 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT19" t="n">
         <v>6.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH19" t="n">
         <v>3.45</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G20" t="n">
         <v>2.8</v>
       </c>
       <c r="H20" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I20" t="n">
         <v>4.1</v>
@@ -5444,40 +5444,40 @@
         <v>2.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M20" t="n">
         <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q20" t="n">
         <v>2.96</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
-        <v>1.06</v>
+        <v>6.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W20" t="n">
         <v>1.56</v>
@@ -5516,7 +5516,7 @@
         <v>36</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
         <v>900</v>
@@ -5528,7 +5528,7 @@
         <v>190</v>
       </c>
       <c r="AM20" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>600</v>
@@ -5537,28 +5537,28 @@
         <v>600</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
         <v>7.4</v>
       </c>
       <c r="AS20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW20" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AX20" t="n">
         <v>6.2</v>
@@ -5567,7 +5567,7 @@
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA20" t="n">
         <v>9.800000000000001</v>
@@ -5576,19 +5576,19 @@
         <v>8.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE20" t="n">
         <v>10</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -5686,10 +5686,10 @@
         <v>3.45</v>
       </c>
       <c r="G21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I21" t="n">
         <v>2.44</v>
@@ -5707,7 +5707,7 @@
         <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
         <v>1.43</v>
@@ -5716,25 +5716,25 @@
         <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R21" t="n">
         <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
         <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V21" t="n">
         <v>1.69</v>
       </c>
       <c r="W21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X21" t="n">
         <v>11</v>
@@ -5776,7 +5776,7 @@
         <v>900</v>
       </c>
       <c r="AK21" t="n">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="AL21" t="n">
         <v>450</v>
@@ -5791,58 +5791,58 @@
         <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR21" t="n">
         <v>6.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
         <v>7.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD21" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>9</v>
-      </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="BH21" t="n">
         <v>3.05</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>4.9</v>
@@ -5994,7 +5994,7 @@
         <v>970</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="Z22" t="n">
         <v>970</v>
@@ -6009,31 +6009,31 @@
         <v>8.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE22" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI22" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -6045,58 +6045,58 @@
         <v>600</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG22" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>5.3</v>
       </c>
       <c r="BH22" t="n">
         <v>3.25</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>1.84</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
         <v>4.3</v>
@@ -6475,7 +6475,7 @@
         <v>1.23</v>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q24" t="n">
         <v>1.69</v>
@@ -6493,7 +6493,7 @@
         <v>2.42</v>
       </c>
       <c r="V24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
@@ -6535,7 +6535,7 @@
         <v>32</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AK24" t="n">
         <v>110</v>
@@ -6547,10 +6547,10 @@
         <v>190</v>
       </c>
       <c r="AN24" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AP24" t="n">
         <v>16</v>
@@ -6583,10 +6583,10 @@
         <v>14.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
         <v>38</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>3.2</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L25" t="n">
         <v>1.53</v>
@@ -6744,7 +6744,7 @@
         <v>2.08</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V25" t="n">
         <v>1.28</v>
@@ -6789,7 +6789,7 @@
         <v>380</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK25" t="n">
         <v>30</v>
@@ -6801,7 +6801,7 @@
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO25" t="n">
         <v>130</v>
@@ -6840,7 +6840,7 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB25" t="n">
         <v>10.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="G26" t="n">
         <v>1.39</v>
@@ -6962,7 +6962,7 @@
         <v>8.6</v>
       </c>
       <c r="I26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
@@ -6977,7 +6977,7 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
         <v>1.13</v>
@@ -6989,13 +6989,13 @@
         <v>1.39</v>
       </c>
       <c r="R26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U26" t="n">
         <v>2.42</v>
@@ -7019,10 +7019,10 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC26" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD26" t="n">
         <v>38</v>
@@ -7031,7 +7031,7 @@
         <v>220</v>
       </c>
       <c r="AF26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG26" t="n">
         <v>11</v>
@@ -7067,7 +7067,7 @@
         <v>26</v>
       </c>
       <c r="AR26" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS26" t="n">
         <v>50</v>
@@ -7079,10 +7079,10 @@
         <v>13.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW26" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -7094,7 +7094,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB26" t="n">
         <v>11.5</v>
@@ -7103,16 +7103,16 @@
         <v>12</v>
       </c>
       <c r="BD26" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE26" t="n">
         <v>46</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH26" t="n">
         <v>5.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7237,10 +7237,10 @@
         <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R27" t="n">
         <v>1.33</v>
@@ -7249,7 +7249,7 @@
         <v>3.35</v>
       </c>
       <c r="T27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U27" t="n">
         <v>1.98</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7467,16 +7467,16 @@
         <v>2.3</v>
       </c>
       <c r="H28" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J28" t="n">
         <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>1.26</v>
@@ -7494,7 +7494,7 @@
         <v>2.34</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R28" t="n">
         <v>1.55</v>
@@ -7632,13 +7632,13 @@
         <v>9</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN28" t="n">
         <v>5.8</v>
@@ -7650,13 +7650,13 @@
         <v>16</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT28" t="n">
         <v>7</v>
@@ -7668,23 +7668,23 @@
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
         <v>3.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L30" t="n">
         <v>1.3</v>
@@ -8011,28 +8011,28 @@
         <v>2.98</v>
       </c>
       <c r="T30" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V30" t="n">
         <v>1.34</v>
       </c>
       <c r="W30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X30" t="n">
         <v>18</v>
       </c>
       <c r="Y30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="n">
         <v>75</v>
       </c>
       <c r="AA30" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB30" t="n">
         <v>11.5</v>
@@ -8041,19 +8041,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE30" t="n">
         <v>190</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI30" t="n">
         <v>250</v>
@@ -8074,7 +8074,7 @@
         <v>14.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP30" t="n">
         <v>14.5</v>
@@ -8086,7 +8086,7 @@
         <v>14.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT30" t="n">
         <v>8.800000000000001</v>
@@ -8098,7 +8098,7 @@
         <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AX30" t="n">
         <v>11</v>
@@ -8107,19 +8107,19 @@
         <v>9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA30" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD30" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BE30" t="n">
         <v>7.2</v>
@@ -8128,10 +8128,10 @@
         <v>11</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI30" t="n">
         <v>3.25</v>
@@ -8140,34 +8140,34 @@
         <v>9.6</v>
       </c>
       <c r="BK30" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP30" t="n">
         <v>15</v>
       </c>
       <c r="BQ30" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT30" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>7.6</v>
       </c>
       <c r="BU30" t="n">
         <v>5.4</v>
@@ -8176,13 +8176,13 @@
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -8235,13 +8235,13 @@
         <v>4.7</v>
       </c>
       <c r="J31" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
         <v>4.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
@@ -8253,25 +8253,25 @@
         <v>1.22</v>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
         <v>1.68</v>
       </c>
       <c r="R31" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S31" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T31" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U31" t="n">
         <v>2.42</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W31" t="n">
         <v>1.99</v>
@@ -8286,7 +8286,7 @@
         <v>36</v>
       </c>
       <c r="AA31" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB31" t="n">
         <v>12.5</v>
@@ -8298,7 +8298,7 @@
         <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF31" t="n">
         <v>14.5</v>
@@ -8310,7 +8310,7 @@
         <v>16</v>
       </c>
       <c r="AI31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ31" t="n">
         <v>23</v>
@@ -8328,7 +8328,7 @@
         <v>10.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AP31" t="n">
         <v>16.5</v>
@@ -8340,19 +8340,19 @@
         <v>25</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AX31" t="n">
         <v>11</v>
@@ -8361,7 +8361,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA31" t="n">
         <v>34</v>
@@ -8370,7 +8370,7 @@
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD31" t="n">
         <v>24</v>
@@ -8382,7 +8382,7 @@
         <v>8.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH31" t="n">
         <v>4.2</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -8480,19 +8480,19 @@
         <v>2.76</v>
       </c>
       <c r="G32" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H32" t="n">
         <v>2.96</v>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J32" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L32" t="n">
         <v>1.61</v>
@@ -8504,10 +8504,10 @@
         <v>2.36</v>
       </c>
       <c r="O32" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P32" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q32" t="n">
         <v>2.8</v>
@@ -8516,19 +8516,19 @@
         <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T32" t="n">
         <v>2.18</v>
       </c>
       <c r="U32" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="V32" t="n">
         <v>1.42</v>
       </c>
       <c r="W32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X32" t="n">
         <v>9.199999999999999</v>
@@ -8555,10 +8555,10 @@
         <v>290</v>
       </c>
       <c r="AF32" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH32" t="n">
         <v>26</v>
@@ -8579,10 +8579,10 @@
         <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO32" t="n">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="AP32" t="n">
         <v>6.6</v>
@@ -8591,13 +8591,13 @@
         <v>6.2</v>
       </c>
       <c r="AR32" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU32" t="n">
         <v>6</v>
@@ -8606,37 +8606,37 @@
         <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY32" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB32" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF32" t="n">
         <v>8.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH32" t="n">
         <v>2.64</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
         <v>4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
@@ -8764,16 +8764,16 @@
         <v>2.22</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R33" t="n">
         <v>1.48</v>
       </c>
       <c r="S33" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T33" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U33" t="n">
         <v>2.38</v>
@@ -8785,7 +8785,7 @@
         <v>1.43</v>
       </c>
       <c r="X33" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y33" t="n">
         <v>15</v>
@@ -8839,10 +8839,10 @@
         <v>15.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR33" t="n">
         <v>12</v>
@@ -8857,13 +8857,13 @@
         <v>8</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AY33" t="n">
         <v>10</v>
@@ -8872,7 +8872,7 @@
         <v>11.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB33" t="n">
         <v>34</v>
@@ -8884,7 +8884,7 @@
         <v>25</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF33" t="n">
         <v>19.5</v>
@@ -8893,68 +8893,68 @@
         <v>11.5</v>
       </c>
       <c r="BH33" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ33" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BN33" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BR33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT33" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV33" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
         <v>3.5</v>
       </c>
       <c r="H34" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I34" t="n">
         <v>2.84</v>
@@ -9033,10 +9033,10 @@
         <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W34" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X34" t="n">
         <v>12.5</v>
@@ -9084,7 +9084,7 @@
         <v>60</v>
       </c>
       <c r="AM34" t="n">
-        <v>440</v>
+        <v>580</v>
       </c>
       <c r="AN34" t="n">
         <v>55</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -9248,13 +9248,13 @@
         <v>2.5</v>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>3.15</v>
       </c>
       <c r="K35" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L35" t="n">
         <v>1.31</v>
@@ -9272,7 +9272,7 @@
         <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="R35" t="n">
         <v>1.43</v>
@@ -9287,10 +9287,10 @@
         <v>2.28</v>
       </c>
       <c r="V35" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W35" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X35" t="n">
         <v>970</v>
@@ -9341,10 +9341,10 @@
         <v>580</v>
       </c>
       <c r="AN35" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO35" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP35" t="n">
         <v>5.4</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -9496,67 +9496,67 @@
         <v>2.66</v>
       </c>
       <c r="G36" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H36" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I36" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K36" t="n">
         <v>4.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P36" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S36" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T36" t="n">
         <v>1.47</v>
       </c>
       <c r="U36" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="V36" t="n">
         <v>1.64</v>
       </c>
       <c r="W36" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X36" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="Y36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA36" t="n">
         <v>42</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>85</v>
       </c>
       <c r="AB36" t="n">
         <v>22</v>
@@ -9565,67 +9565,67 @@
         <v>11.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE36" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AF36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI36" t="n">
         <v>42</v>
       </c>
-      <c r="AG36" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>75</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AK36" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AL36" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AM36" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AN36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO36" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ36" t="n">
         <v>13</v>
       </c>
-      <c r="AQ36" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AR36" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AT36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW36" t="n">
         <v>17</v>
       </c>
       <c r="AX36" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY36" t="n">
         <v>10.5</v>
@@ -9637,64 +9637,64 @@
         <v>20</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BC36" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BE36" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BF36" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH36" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI36" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BJ36" t="n">
         <v>8.6</v>
       </c>
       <c r="BK36" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN36" t="n">
         <v>6.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BP36" t="n">
         <v>19</v>
       </c>
       <c r="BQ36" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR36" t="n">
         <v>25</v>
       </c>
       <c r="BS36" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT36" t="n">
         <v>6.4</v>
       </c>
       <c r="BU36" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV36" t="n">
         <v>17</v>
@@ -9706,7 +9706,7 @@
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G37" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H37" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="I37" t="n">
         <v>2.16</v>
       </c>
       <c r="J37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K37" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L37" t="n">
         <v>1.34</v>
@@ -9780,7 +9780,7 @@
         <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R37" t="n">
         <v>1.42</v>
@@ -9798,7 +9798,7 @@
         <v>1.86</v>
       </c>
       <c r="W37" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X37" t="n">
         <v>22</v>
@@ -9870,7 +9870,7 @@
         <v>13.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV37" t="n">
         <v>8.800000000000001</v>
@@ -9888,22 +9888,22 @@
         <v>15</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB37" t="n">
         <v>5.1</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE37" t="n">
         <v>5.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG37" t="n">
         <v>11</v>
@@ -9918,7 +9918,7 @@
         <v>9.6</v>
       </c>
       <c r="BK37" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
@@ -9930,7 +9930,7 @@
         <v>7.4</v>
       </c>
       <c r="BO37" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BP37" t="n">
         <v>30</v>
@@ -9948,7 +9948,7 @@
         <v>5.3</v>
       </c>
       <c r="BU37" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BV37" t="n">
         <v>15.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>2.74</v>
       </c>
       <c r="G38" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H38" t="n">
         <v>2.38</v>
@@ -10052,10 +10052,10 @@
         <v>1.59</v>
       </c>
       <c r="W38" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X38" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y38" t="n">
         <v>14</v>
@@ -10070,7 +10070,7 @@
         <v>970</v>
       </c>
       <c r="AC38" t="n">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
         <v>13.5</v>
@@ -10079,7 +10079,7 @@
         <v>500</v>
       </c>
       <c r="AF38" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AG38" t="n">
         <v>970</v>
@@ -10103,7 +10103,7 @@
         <v>580</v>
       </c>
       <c r="AN38" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO38" t="n">
         <v>21</v>
@@ -10112,7 +10112,7 @@
         <v>5.6</v>
       </c>
       <c r="AQ38" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AR38" t="n">
         <v>5.5</v>
@@ -10160,13 +10160,13 @@
         <v>6</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH38" t="n">
         <v>3.9</v>
       </c>
       <c r="BI38" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BJ38" t="n">
         <v>9.4</v>
@@ -10208,7 +10208,7 @@
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -10255,19 +10255,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G39" t="n">
         <v>2.06</v>
       </c>
       <c r="H39" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I39" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K39" t="n">
         <v>5</v>
@@ -10303,10 +10303,10 @@
         <v>2.86</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X39" t="n">
         <v>40</v>
@@ -10366,13 +10366,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ39" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS39" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT39" t="n">
         <v>13</v>
@@ -10384,7 +10384,7 @@
         <v>12</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AX39" t="n">
         <v>13</v>
@@ -10396,7 +10396,7 @@
         <v>10.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BB39" t="n">
         <v>17.5</v>
@@ -10405,16 +10405,16 @@
         <v>12.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF39" t="n">
         <v>5.9</v>
       </c>
       <c r="BG39" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BH39" t="n">
         <v>5.6</v>
@@ -10426,7 +10426,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK39" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
@@ -10438,13 +10438,13 @@
         <v>5.9</v>
       </c>
       <c r="BO39" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP39" t="n">
         <v>13</v>
       </c>
       <c r="BQ39" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR39" t="n">
         <v>19</v>
@@ -10456,7 +10456,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU39" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BV39" t="n">
         <v>25</v>
@@ -10474,11 +10474,11 @@
         <v>11.5</v>
       </c>
       <c r="CA39" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -10509,22 +10509,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G40" t="n">
         <v>2.56</v>
       </c>
       <c r="H40" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I40" t="n">
         <v>3.15</v>
       </c>
       <c r="J40" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K40" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L40" t="n">
         <v>1.29</v>
@@ -10533,7 +10533,7 @@
         <v>1.04</v>
       </c>
       <c r="N40" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O40" t="n">
         <v>1.23</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
         <v>1.47</v>
       </c>
       <c r="G41" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H41" t="n">
         <v>6</v>
@@ -10778,7 +10778,7 @@
         <v>4.7</v>
       </c>
       <c r="K41" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.24</v>
@@ -10796,10 +10796,10 @@
         <v>2.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S41" t="n">
         <v>2.26</v>
@@ -10814,7 +10814,7 @@
         <v>1.15</v>
       </c>
       <c r="W41" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="X41" t="n">
         <v>50</v>
@@ -10856,7 +10856,7 @@
         <v>500</v>
       </c>
       <c r="AK41" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL41" t="n">
         <v>500</v>
@@ -10874,10 +10874,10 @@
         <v>6.2</v>
       </c>
       <c r="AQ41" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS41" t="n">
         <v>4.2</v>
@@ -10889,10 +10889,10 @@
         <v>5.8</v>
       </c>
       <c r="AV41" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW41" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX41" t="n">
         <v>6.4</v>
@@ -10901,28 +10901,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BA41" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="BC41" t="n">
         <v>8.4</v>
       </c>
       <c r="BD41" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE41" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF41" t="n">
         <v>4.8</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BH41" t="n">
         <v>4.7</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -11017,13 +11017,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G42" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I42" t="n">
         <v>5</v>
@@ -11050,16 +11050,16 @@
         <v>2.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R42" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S42" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U42" t="n">
         <v>2.46</v>
@@ -11074,7 +11074,7 @@
         <v>32</v>
       </c>
       <c r="Y42" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Z42" t="n">
         <v>44</v>
@@ -11086,7 +11086,7 @@
         <v>16</v>
       </c>
       <c r="AC42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD42" t="n">
         <v>23</v>
@@ -11098,13 +11098,13 @@
         <v>14.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH42" t="n">
         <v>17.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ42" t="n">
         <v>21</v>
@@ -11116,67 +11116,67 @@
         <v>28</v>
       </c>
       <c r="AM42" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN42" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO42" t="n">
         <v>44</v>
       </c>
       <c r="AP42" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AQ42" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AS42" t="n">
-        <v>5.7</v>
+        <v>28</v>
       </c>
       <c r="AT42" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW42" t="n">
         <v>36</v>
       </c>
       <c r="AX42" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.4</v>
+        <v>29</v>
       </c>
       <c r="BB42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC42" t="n">
         <v>14</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>12</v>
       </c>
       <c r="BD42" t="n">
         <v>19</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="BF42" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG42" t="n">
-        <v>5.3</v>
+        <v>23</v>
       </c>
       <c r="BH42" t="n">
         <v>4.6</v>
@@ -11194,7 +11194,7 @@
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN42" t="n">
         <v>5.1</v>
@@ -11212,7 +11212,7 @@
         <v>22</v>
       </c>
       <c r="BS42" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT42" t="n">
         <v>8.800000000000001</v>
@@ -11230,7 +11230,7 @@
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
         <v>2.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R43" t="n">
         <v>1.53</v>
@@ -11325,13 +11325,13 @@
         <v>1.83</v>
       </c>
       <c r="X43" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="Y43" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z43" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AA43" t="n">
         <v>900</v>
@@ -11343,52 +11343,52 @@
         <v>11</v>
       </c>
       <c r="AD43" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AE43" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AF43" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AG43" t="n">
         <v>12.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI43" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ43" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AK43" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AL43" t="n">
         <v>500</v>
       </c>
       <c r="AM43" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN43" t="n">
-        <v>55</v>
+        <v>13.5</v>
       </c>
       <c r="AO43" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AP43" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR43" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.7</v>
+        <v>44</v>
       </c>
       <c r="AT43" t="n">
         <v>9.800000000000001</v>
@@ -11397,10 +11397,10 @@
         <v>7.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="AX43" t="n">
         <v>12</v>
@@ -11412,28 +11412,28 @@
         <v>12</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="BB43" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BC43" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BD43" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF43" t="n">
         <v>8.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="BH43" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI43" t="n">
         <v>3.3</v>
@@ -11442,13 +11442,13 @@
         <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>11</v>
+        <v>3.05</v>
       </c>
       <c r="BN43" t="n">
         <v>5.3</v>
@@ -11460,13 +11460,13 @@
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT43" t="n">
         <v>7.2</v>
@@ -11478,13 +11478,13 @@
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>8.6</v>
+        <v>2.84</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>9.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="BZ43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -11525,25 +11525,25 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G44" t="n">
         <v>2.24</v>
       </c>
       <c r="H44" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J44" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L44" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="M44" t="n">
         <v>1.02</v>
@@ -11555,16 +11555,16 @@
         <v>1.13</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R44" t="n">
         <v>1.95</v>
       </c>
       <c r="S44" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T44" t="n">
         <v>1.43</v>
@@ -11576,19 +11576,19 @@
         <v>1.42</v>
       </c>
       <c r="W44" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X44" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="Y44" t="n">
         <v>25</v>
       </c>
       <c r="Z44" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AA44" t="n">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="AB44" t="n">
         <v>20</v>
@@ -11615,7 +11615,7 @@
         <v>34</v>
       </c>
       <c r="AJ44" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK44" t="n">
         <v>23</v>
@@ -11624,7 +11624,7 @@
         <v>23</v>
       </c>
       <c r="AM44" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN44" t="n">
         <v>8.6</v>
@@ -11633,19 +11633,19 @@
         <v>16</v>
       </c>
       <c r="AP44" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AS44" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AT44" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU44" t="n">
         <v>9.6</v>
@@ -11654,10 +11654,10 @@
         <v>12</v>
       </c>
       <c r="AW44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX44" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY44" t="n">
         <v>10</v>
@@ -11669,16 +11669,16 @@
         <v>20</v>
       </c>
       <c r="BB44" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC44" t="n">
         <v>13.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BE44" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BF44" t="n">
         <v>6.6</v>
@@ -11687,25 +11687,25 @@
         <v>10.5</v>
       </c>
       <c r="BH44" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI44" t="n">
         <v>4.2</v>
       </c>
       <c r="BJ44" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK44" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BN44" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO44" t="n">
         <v>4.5</v>
@@ -11714,13 +11714,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ44" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR44" t="n">
         <v>18.5</v>
       </c>
       <c r="BS44" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT44" t="n">
         <v>7.6</v>
@@ -11732,13 +11732,13 @@
         <v>21</v>
       </c>
       <c r="BW44" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX44" t="n">
         <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BZ44" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G45" t="n">
         <v>3.9</v>
       </c>
       <c r="H45" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I45" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="J45" t="n">
         <v>4.2</v>
       </c>
       <c r="K45" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L45" t="n">
         <v>1.2</v>
@@ -11809,31 +11809,31 @@
         <v>1.14</v>
       </c>
       <c r="P45" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R45" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S45" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
         <v>1.46</v>
       </c>
       <c r="U45" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="V45" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="W45" t="n">
         <v>1.34</v>
       </c>
       <c r="X45" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="Y45" t="n">
         <v>21</v>
@@ -11842,7 +11842,7 @@
         <v>22</v>
       </c>
       <c r="AA45" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB45" t="n">
         <v>500</v>
@@ -11851,103 +11851,103 @@
         <v>14</v>
       </c>
       <c r="AD45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE45" t="n">
         <v>22</v>
       </c>
       <c r="AF45" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AG45" t="n">
         <v>21</v>
       </c>
       <c r="AH45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI45" t="n">
         <v>28</v>
       </c>
       <c r="AJ45" t="n">
+        <v>470</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL45" t="n">
         <v>500</v>
       </c>
-      <c r="AK45" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL45" t="n">
+      <c r="AM45" t="n">
         <v>60</v>
       </c>
-      <c r="AM45" t="n">
-        <v>200</v>
-      </c>
       <c r="AN45" t="n">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="AO45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="AQ45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV45" t="n">
         <v>9</v>
       </c>
-      <c r="AR45" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AW45" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX45" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AY45" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ45" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="BB45" t="n">
-        <v>5.2</v>
+        <v>46</v>
       </c>
       <c r="BC45" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="BD45" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE45" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH45" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>5.2</v>
       </c>
       <c r="BI45" t="n">
         <v>3.95</v>
       </c>
       <c r="BJ45" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK45" t="n">
         <v>6.2</v>
@@ -11956,25 +11956,25 @@
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN45" t="n">
         <v>7.8</v>
       </c>
       <c r="BO45" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT45" t="n">
         <v>5.6</v>
@@ -11983,7 +11983,7 @@
         <v>4.9</v>
       </c>
       <c r="BV45" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW45" t="n">
         <v>7.8</v>
@@ -11992,7 +11992,7 @@
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ45" t="n">
         <v>0</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -12033,13 +12033,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G46" t="n">
         <v>2.22</v>
       </c>
       <c r="H46" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="I46" t="n">
         <v>3.85</v>
@@ -12048,7 +12048,7 @@
         <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L46" t="n">
         <v>1.17</v>
@@ -12063,7 +12063,7 @@
         <v>1.1</v>
       </c>
       <c r="P46" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q46" t="n">
         <v>1.32</v>
@@ -12072,7 +12072,7 @@
         <v>1.9</v>
       </c>
       <c r="S46" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T46" t="n">
         <v>1.37</v>
@@ -12135,128 +12135,128 @@
         <v>500</v>
       </c>
       <c r="AN46" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AO46" t="n">
         <v>970</v>
       </c>
       <c r="AP46" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT46" t="n">
         <v>2.14</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>2.06</v>
       </c>
       <c r="AU46" t="n">
         <v>2.5</v>
       </c>
       <c r="AV46" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BC46" t="n">
         <v>2.18</v>
       </c>
-      <c r="AW46" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB46" t="n">
+      <c r="BD46" t="n">
         <v>2.2</v>
       </c>
-      <c r="BC46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BE46" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="BF46" t="n">
         <v>3.4</v>
       </c>
       <c r="BG46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK46" t="n">
         <v>2.02</v>
       </c>
-      <c r="BH46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK46" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BN46" t="n">
         <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP46" t="n">
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BV46" t="n">
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BZ46" t="n">
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
         <v>1.99</v>
       </c>
       <c r="H47" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
         <v>5.2</v>
@@ -12305,7 +12305,7 @@
         <v>4.1</v>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
@@ -12320,13 +12320,13 @@
         <v>1.89</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="R47" t="n">
         <v>1.34</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T47" t="n">
         <v>1.81</v>
@@ -12362,7 +12362,7 @@
         <v>19.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AF47" t="n">
         <v>12</v>
@@ -12374,7 +12374,7 @@
         <v>20</v>
       </c>
       <c r="AI47" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AJ47" t="n">
         <v>26</v>
@@ -12392,7 +12392,7 @@
         <v>14</v>
       </c>
       <c r="AO47" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AP47" t="n">
         <v>5.1</v>
@@ -12494,13 +12494,13 @@
         <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>2.52</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>2.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
         <v>2.42</v>
       </c>
       <c r="G48" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H48" t="n">
         <v>3.1</v>
@@ -12556,10 +12556,10 @@
         <v>3.1</v>
       </c>
       <c r="K48" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L48" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M48" t="n">
         <v>1.09</v>
@@ -12583,16 +12583,16 @@
         <v>4.1</v>
       </c>
       <c r="T48" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U48" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W48" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X48" t="n">
         <v>12</v>
@@ -12604,7 +12604,7 @@
         <v>23</v>
       </c>
       <c r="AA48" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AB48" t="n">
         <v>9.4</v>
@@ -12628,7 +12628,7 @@
         <v>24</v>
       </c>
       <c r="AI48" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AJ48" t="n">
         <v>46</v>
@@ -12640,7 +12640,7 @@
         <v>60</v>
       </c>
       <c r="AM48" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN48" t="n">
         <v>34</v>
@@ -12655,22 +12655,22 @@
         <v>9.6</v>
       </c>
       <c r="AR48" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AS48" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AT48" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AU48" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV48" t="n">
         <v>12</v>
       </c>
       <c r="AW48" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AX48" t="n">
         <v>13.5</v>
@@ -12679,46 +12679,46 @@
         <v>10</v>
       </c>
       <c r="AZ48" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA48" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BB48" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BC48" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BD48" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF48" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BG48" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BH48" t="n">
         <v>3.15</v>
       </c>
       <c r="BI48" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ48" t="n">
         <v>10.5</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN48" t="n">
         <v>5.4</v>
@@ -12730,13 +12730,13 @@
         <v>21</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT48" t="n">
         <v>6.4</v>
@@ -12748,23 +12748,23 @@
         <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G49" t="n">
         <v>12.5</v>
@@ -12810,7 +12810,7 @@
         <v>5.9</v>
       </c>
       <c r="K49" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L49" t="n">
         <v>1.28</v>
@@ -12819,7 +12819,7 @@
         <v>1.04</v>
       </c>
       <c r="N49" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O49" t="n">
         <v>1.21</v>
@@ -12834,13 +12834,13 @@
         <v>1.58</v>
       </c>
       <c r="S49" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T49" t="n">
         <v>2.06</v>
       </c>
       <c r="U49" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V49" t="n">
         <v>4</v>
@@ -12852,10 +12852,10 @@
         <v>25</v>
       </c>
       <c r="Y49" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z49" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA49" t="n">
         <v>10.5</v>
@@ -12870,10 +12870,10 @@
         <v>11</v>
       </c>
       <c r="AE49" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AF49" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="AG49" t="n">
         <v>44</v>
@@ -12891,7 +12891,7 @@
         <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="AM49" t="n">
         <v>1000</v>
@@ -12915,7 +12915,7 @@
         <v>9.4</v>
       </c>
       <c r="AT49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU49" t="n">
         <v>12</v>
@@ -12939,19 +12939,19 @@
         <v>30</v>
       </c>
       <c r="BB49" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="BC49" t="n">
-        <v>44</v>
+        <v>12.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="BE49" t="n">
-        <v>70</v>
+        <v>12.5</v>
       </c>
       <c r="BF49" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="BG49" t="n">
         <v>4.5</v>
@@ -12966,7 +12966,7 @@
         <v>12.5</v>
       </c>
       <c r="BK49" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
@@ -12978,7 +12978,7 @@
         <v>14.5</v>
       </c>
       <c r="BO49" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
@@ -12990,7 +12990,7 @@
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT49" t="n">
         <v>3.95</v>
@@ -13008,7 +13008,7 @@
         <v>24</v>
       </c>
       <c r="BY49" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
         <v>4.7</v>
       </c>
       <c r="O50" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P50" t="n">
         <v>2.22</v>
@@ -13100,10 +13100,10 @@
         <v>1.46</v>
       </c>
       <c r="W50" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X50" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y50" t="n">
         <v>15.5</v>
@@ -13115,7 +13115,7 @@
         <v>55</v>
       </c>
       <c r="AB50" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC50" t="n">
         <v>8.6</v>
@@ -13151,7 +13151,7 @@
         <v>70</v>
       </c>
       <c r="AN50" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO50" t="n">
         <v>27</v>
@@ -13166,7 +13166,7 @@
         <v>20</v>
       </c>
       <c r="AS50" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT50" t="n">
         <v>11.5</v>
@@ -13187,7 +13187,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA50" t="n">
         <v>32</v>
@@ -13205,7 +13205,7 @@
         <v>60</v>
       </c>
       <c r="BF50" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG50" t="n">
         <v>21</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -13303,67 +13303,67 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="G51" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="H51" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J51" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K51" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L51" t="n">
         <v>1.51</v>
       </c>
       <c r="M51" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O51" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P51" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="R51" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S51" t="n">
         <v>4.5</v>
       </c>
       <c r="T51" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U51" t="n">
         <v>1.84</v>
       </c>
       <c r="V51" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W51" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="X51" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y51" t="n">
         <v>16</v>
       </c>
       <c r="Z51" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA51" t="n">
         <v>900</v>
@@ -13375,13 +13375,13 @@
         <v>9</v>
       </c>
       <c r="AD51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE51" t="n">
         <v>190</v>
       </c>
       <c r="AF51" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG51" t="n">
         <v>12.5</v>
@@ -13393,7 +13393,7 @@
         <v>110</v>
       </c>
       <c r="AJ51" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK51" t="n">
         <v>28</v>
@@ -13405,7 +13405,7 @@
         <v>580</v>
       </c>
       <c r="AN51" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AO51" t="n">
         <v>700</v>
@@ -13420,10 +13420,10 @@
         <v>29</v>
       </c>
       <c r="AS51" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT51" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU51" t="n">
         <v>7.2</v>
@@ -13432,55 +13432,55 @@
         <v>17.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX51" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY51" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AZ51" t="n">
         <v>20</v>
       </c>
       <c r="BA51" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BC51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD51" t="n">
         <v>36</v>
       </c>
       <c r="BE51" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF51" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH51" t="n">
         <v>2.98</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ51" t="n">
         <v>11</v>
       </c>
       <c r="BK51" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN51" t="n">
         <v>4.4</v>
@@ -13495,7 +13495,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR51" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BS51" t="n">
         <v>11.5</v>
@@ -13504,19 +13504,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU51" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV51" t="n">
         <v>50</v>
       </c>
       <c r="BW51" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX51" t="n">
         <v>90</v>
       </c>
       <c r="BY51" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ51" t="n">
         <v>34</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G52" t="n">
         <v>1.55</v>
@@ -13572,7 +13572,7 @@
         <v>5.5</v>
       </c>
       <c r="K52" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L52" t="n">
         <v>1.13</v>
@@ -13581,7 +13581,7 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="O52" t="n">
         <v>1.07</v>
@@ -13722,65 +13722,65 @@
         <v>7.4</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ52" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN52" t="n">
         <v>5.7</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP52" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR52" t="n">
         <v>15</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT52" t="n">
         <v>11.5</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ52" t="n">
         <v>7.2</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -13811,19 +13811,19 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G53" t="n">
         <v>1.72</v>
       </c>
       <c r="H53" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I53" t="n">
         <v>5.4</v>
       </c>
       <c r="J53" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K53" t="n">
         <v>5.9</v>
@@ -13847,13 +13847,13 @@
         <v>1.3</v>
       </c>
       <c r="R53" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S53" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="T53" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U53" t="n">
         <v>2.88</v>
@@ -13862,7 +13862,7 @@
         <v>1.22</v>
       </c>
       <c r="W53" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X53" t="n">
         <v>55</v>
@@ -13874,7 +13874,7 @@
         <v>65</v>
       </c>
       <c r="AA53" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB53" t="n">
         <v>22</v>
@@ -13937,7 +13937,7 @@
         <v>5.3</v>
       </c>
       <c r="AV53" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW53" t="n">
         <v>7</v>
@@ -13949,7 +13949,7 @@
         <v>4.9</v>
       </c>
       <c r="AZ53" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA53" t="n">
         <v>6.6</v>
@@ -13958,7 +13958,7 @@
         <v>5.8</v>
       </c>
       <c r="BC53" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD53" t="n">
         <v>5.9</v>
@@ -13967,7 +13967,7 @@
         <v>7</v>
       </c>
       <c r="BF53" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BG53" t="n">
         <v>6.2</v>
@@ -13976,65 +13976,65 @@
         <v>6.4</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ53" t="n">
         <v>9</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN53" t="n">
         <v>5.6</v>
       </c>
       <c r="BO53" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP53" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR53" t="n">
         <v>16.5</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT53" t="n">
         <v>10</v>
       </c>
       <c r="BU53" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV53" t="n">
         <v>32</v>
       </c>
       <c r="BW53" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX53" t="n">
         <v>29</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ53" t="n">
         <v>9</v>
       </c>
       <c r="CA53" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
         <v>1.63</v>
       </c>
       <c r="G54" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H54" t="n">
         <v>4.6</v>
@@ -14083,34 +14083,34 @@
         <v>5.3</v>
       </c>
       <c r="L54" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M54" t="n">
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O54" t="n">
         <v>1.13</v>
       </c>
       <c r="P54" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R54" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S54" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="T54" t="n">
         <v>1.49</v>
       </c>
       <c r="U54" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V54" t="n">
         <v>1.23</v>
@@ -14119,10 +14119,10 @@
         <v>2.34</v>
       </c>
       <c r="X54" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="Y54" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="Z54" t="n">
         <v>500</v>
@@ -14146,7 +14146,7 @@
         <v>18.5</v>
       </c>
       <c r="AG54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AH54" t="n">
         <v>25</v>
@@ -14176,13 +14176,13 @@
         <v>16</v>
       </c>
       <c r="AQ54" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR54" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS54" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT54" t="n">
         <v>9</v>
@@ -14191,7 +14191,7 @@
         <v>10.5</v>
       </c>
       <c r="AV54" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AW54" t="n">
         <v>32</v>
@@ -14203,16 +14203,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ54" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB54" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BC54" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BD54" t="n">
         <v>18</v>
@@ -14224,13 +14224,13 @@
         <v>4.8</v>
       </c>
       <c r="BG54" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH54" t="n">
         <v>5.5</v>
       </c>
       <c r="BI54" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BJ54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -14319,13 +14319,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G55" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H55" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I55" t="n">
         <v>4.3</v>
@@ -14334,10 +14334,10 @@
         <v>4.3</v>
       </c>
       <c r="K55" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L55" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M55" t="n">
         <v>1.02</v>
@@ -14355,28 +14355,28 @@
         <v>1.41</v>
       </c>
       <c r="R55" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S55" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T55" t="n">
         <v>1.56</v>
       </c>
       <c r="U55" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V55" t="n">
         <v>1.3</v>
       </c>
       <c r="W55" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X55" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="Y55" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Z55" t="n">
         <v>140</v>
@@ -14394,7 +14394,7 @@
         <v>21</v>
       </c>
       <c r="AE55" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AF55" t="n">
         <v>19</v>
@@ -14409,7 +14409,7 @@
         <v>95</v>
       </c>
       <c r="AJ55" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="AK55" t="n">
         <v>19.5</v>
@@ -14418,37 +14418,37 @@
         <v>28</v>
       </c>
       <c r="AM55" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN55" t="n">
         <v>8</v>
       </c>
       <c r="AO55" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AP55" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ55" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AR55" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT55" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AU55" t="n">
         <v>9</v>
       </c>
       <c r="AV55" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW55" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AX55" t="n">
         <v>12.5</v>
@@ -14457,13 +14457,13 @@
         <v>8.6</v>
       </c>
       <c r="AZ55" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BA55" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BB55" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BC55" t="n">
         <v>13</v>
@@ -14472,13 +14472,13 @@
         <v>18</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="BF55" t="n">
         <v>6</v>
       </c>
       <c r="BG55" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BH55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14585,7 @@
         <v>1000</v>
       </c>
       <c r="J56" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K56" t="n">
         <v>1000</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -14836,10 +14836,10 @@
         <v>1.79</v>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K57" t="n">
         <v>5</v>
@@ -14947,7 +14947,7 @@
         <v>21</v>
       </c>
       <c r="AT57" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU57" t="n">
         <v>10</v>
@@ -14971,16 +14971,16 @@
         <v>18</v>
       </c>
       <c r="BB57" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC57" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE57" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BF57" t="n">
         <v>14</v>
@@ -14998,7 +14998,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK57" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BL57" t="n">
         <v>60</v>
@@ -15010,7 +15010,7 @@
         <v>8.6</v>
       </c>
       <c r="BO57" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BP57" t="n">
         <v>26</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -15081,13 +15081,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G58" t="n">
         <v>3.35</v>
       </c>
       <c r="H58" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I58" t="n">
         <v>3.05</v>
@@ -15096,7 +15096,7 @@
         <v>2.82</v>
       </c>
       <c r="K58" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L58" t="n">
         <v>1.48</v>
@@ -15105,13 +15105,13 @@
         <v>1.12</v>
       </c>
       <c r="N58" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O58" t="n">
         <v>1.48</v>
       </c>
       <c r="P58" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q58" t="n">
         <v>2.5</v>
@@ -15123,19 +15123,19 @@
         <v>5.2</v>
       </c>
       <c r="T58" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U58" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V58" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W58" t="n">
         <v>1.42</v>
       </c>
       <c r="X58" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Y58" t="n">
         <v>970</v>
@@ -15195,10 +15195,10 @@
         <v>6.2</v>
       </c>
       <c r="AR58" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS58" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AT58" t="n">
         <v>7.2</v>
@@ -15207,13 +15207,13 @@
         <v>4.2</v>
       </c>
       <c r="AV58" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW58" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AX58" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY58" t="n">
         <v>9.6</v>
@@ -15222,25 +15222,25 @@
         <v>7.2</v>
       </c>
       <c r="BA58" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB58" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC58" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD58" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BE58" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="BF58" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG58" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH58" t="n">
         <v>2.84</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
         <v>3.85</v>
       </c>
       <c r="L59" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="M59" t="n">
         <v>1.06</v>
@@ -15377,7 +15377,7 @@
         <v>3</v>
       </c>
       <c r="T59" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U59" t="n">
         <v>2.32</v>
@@ -15452,19 +15452,19 @@
         <v>14</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.9</v>
+        <v>18.5</v>
       </c>
       <c r="AT59" t="n">
         <v>10.5</v>
       </c>
       <c r="AU59" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV59" t="n">
         <v>10.5</v>
       </c>
       <c r="AW59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX59" t="n">
         <v>16.5</v>
@@ -15476,16 +15476,16 @@
         <v>13.5</v>
       </c>
       <c r="BA59" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB59" t="n">
         <v>18</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>6</v>
       </c>
       <c r="BC59" t="n">
         <v>21</v>
       </c>
       <c r="BD59" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE59" t="n">
         <v>6.4</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G60" t="n">
         <v>4.1</v>
@@ -15622,7 +15622,7 @@
         <v>1.97</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R60" t="n">
         <v>1.35</v>
@@ -15631,7 +15631,7 @@
         <v>3.45</v>
       </c>
       <c r="T60" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="U60" t="n">
         <v>2.08</v>
@@ -15709,7 +15709,7 @@
         <v>21</v>
       </c>
       <c r="AT60" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU60" t="n">
         <v>7</v>
@@ -15721,7 +15721,7 @@
         <v>17.5</v>
       </c>
       <c r="AX60" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY60" t="n">
         <v>12</v>
@@ -15730,16 +15730,16 @@
         <v>15.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BB60" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC60" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BD60" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE60" t="n">
         <v>9</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -15852,13 +15852,13 @@
         <v>1.94</v>
       </c>
       <c r="I61" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J61" t="n">
         <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L61" t="n">
         <v>1.53</v>
@@ -15882,7 +15882,7 @@
         <v>1.19</v>
       </c>
       <c r="S61" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T61" t="n">
         <v>2.1</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
         <v>3.45</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="R62" t="n">
         <v>2.14</v>
@@ -16205,13 +16205,13 @@
         <v>300</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.96</v>
+        <v>5.6</v>
       </c>
       <c r="AQ62" t="n">
         <v>5.4</v>
       </c>
       <c r="AR62" t="n">
-        <v>2.96</v>
+        <v>5.6</v>
       </c>
       <c r="AS62" t="n">
         <v>2.86</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -16351,22 +16351,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="G63" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="H63" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J63" t="n">
         <v>4.7</v>
       </c>
       <c r="K63" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L63" t="n">
         <v>1.18</v>
@@ -16375,34 +16375,34 @@
         <v>1.02</v>
       </c>
       <c r="N63" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O63" t="n">
         <v>1.13</v>
       </c>
       <c r="P63" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R63" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S63" t="n">
         <v>1.94</v>
       </c>
       <c r="T63" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U63" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="V63" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W63" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="X63" t="n">
         <v>46</v>
@@ -16417,10 +16417,10 @@
         <v>120</v>
       </c>
       <c r="AB63" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD63" t="n">
         <v>24</v>
@@ -16435,40 +16435,40 @@
         <v>13</v>
       </c>
       <c r="AH63" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI63" t="n">
         <v>50</v>
       </c>
       <c r="AJ63" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AK63" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL63" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM63" t="n">
         <v>65</v>
       </c>
       <c r="AN63" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AO63" t="n">
         <v>34</v>
       </c>
       <c r="AP63" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AQ63" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AR63" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="AS63" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT63" t="n">
         <v>15</v>
@@ -16480,7 +16480,7 @@
         <v>18</v>
       </c>
       <c r="AW63" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX63" t="n">
         <v>13.5</v>
@@ -16495,7 +16495,7 @@
         <v>30</v>
       </c>
       <c r="BB63" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC63" t="n">
         <v>11</v>
@@ -16504,10 +16504,10 @@
         <v>16.5</v>
       </c>
       <c r="BE63" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF63" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG63" t="n">
         <v>21</v>
@@ -16519,25 +16519,25 @@
         <v>4.1</v>
       </c>
       <c r="BJ63" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK63" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN63" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO63" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP63" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ63" t="n">
         <v>6</v>
@@ -16546,25 +16546,25 @@
         <v>17.5</v>
       </c>
       <c r="BS63" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT63" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU63" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV63" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW63" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX63" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY63" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ63" t="n">
         <v>0</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16605,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G64" t="n">
         <v>2.76</v>
@@ -16614,7 +16614,7 @@
         <v>2.8</v>
       </c>
       <c r="I64" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J64" t="n">
         <v>3.55</v>
@@ -16650,10 +16650,10 @@
         <v>1.75</v>
       </c>
       <c r="U64" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V64" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W64" t="n">
         <v>1.56</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -16868,7 +16868,7 @@
         <v>3.35</v>
       </c>
       <c r="I65" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J65" t="n">
         <v>3.6</v>
@@ -16889,7 +16889,7 @@
         <v>1.31</v>
       </c>
       <c r="P65" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
         <v>1.89</v>
@@ -16898,7 +16898,7 @@
         <v>1.4</v>
       </c>
       <c r="S65" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T65" t="n">
         <v>1.75</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="Z65" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA65" t="n">
         <v>70</v>
@@ -17009,34 +17009,34 @@
         <v>20</v>
       </c>
       <c r="BD65" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE65" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF65" t="n">
         <v>15</v>
       </c>
       <c r="BG65" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH65" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI65" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ65" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK65" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL65" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM65" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN65" t="n">
         <v>5.4</v>
@@ -17060,19 +17060,19 @@
         <v>7</v>
       </c>
       <c r="BU65" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV65" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW65" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX65" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY65" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ65" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -17158,7 +17158,7 @@
         <v>1.11</v>
       </c>
       <c r="U66" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V66" t="n">
         <v>1.01</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -17621,16 +17621,16 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G68" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H68" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I68" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>3.75</v>
@@ -17639,7 +17639,7 @@
         <v>3.95</v>
       </c>
       <c r="L68" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M68" t="n">
         <v>1.06</v>
@@ -17651,7 +17651,7 @@
         <v>1.28</v>
       </c>
       <c r="P68" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q68" t="n">
         <v>1.83</v>
@@ -17660,19 +17660,19 @@
         <v>1.41</v>
       </c>
       <c r="S68" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T68" t="n">
         <v>1.74</v>
       </c>
       <c r="U68" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V68" t="n">
         <v>1.33</v>
       </c>
       <c r="W68" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X68" t="n">
         <v>17</v>
@@ -17681,10 +17681,10 @@
         <v>16</v>
       </c>
       <c r="Z68" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA68" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB68" t="n">
         <v>10.5</v>
@@ -17696,7 +17696,7 @@
         <v>16.5</v>
       </c>
       <c r="AE68" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF68" t="n">
         <v>13.5</v>
@@ -17705,7 +17705,7 @@
         <v>11</v>
       </c>
       <c r="AH68" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI68" t="n">
         <v>55</v>
@@ -17717,16 +17717,16 @@
         <v>22</v>
       </c>
       <c r="AL68" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM68" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN68" t="n">
         <v>14</v>
       </c>
       <c r="AO68" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP68" t="n">
         <v>13</v>
@@ -17738,7 +17738,7 @@
         <v>21</v>
       </c>
       <c r="AS68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT68" t="n">
         <v>9</v>
@@ -17750,7 +17750,7 @@
         <v>13.5</v>
       </c>
       <c r="AW68" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX68" t="n">
         <v>11.5</v>
@@ -17762,7 +17762,7 @@
         <v>15.5</v>
       </c>
       <c r="BA68" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB68" t="n">
         <v>20</v>
@@ -17771,22 +17771,22 @@
         <v>18</v>
       </c>
       <c r="BD68" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BE68" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF68" t="n">
         <v>12</v>
       </c>
       <c r="BG68" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH68" t="n">
         <v>3.75</v>
       </c>
       <c r="BI68" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="BJ68" t="n">
         <v>9.800000000000001</v>
@@ -17798,19 +17798,19 @@
         <v>1000</v>
       </c>
       <c r="BM68" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN68" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO68" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP68" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ68" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR68" t="n">
         <v>28</v>
@@ -17819,13 +17819,13 @@
         <v>7.6</v>
       </c>
       <c r="BT68" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU68" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BV68" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW68" t="n">
         <v>8</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -17878,7 +17878,7 @@
         <v>2.16</v>
       </c>
       <c r="G69" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H69" t="n">
         <v>2.88</v>
@@ -17905,7 +17905,7 @@
         <v>1.14</v>
       </c>
       <c r="P69" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q69" t="n">
         <v>1.43</v>
@@ -17920,13 +17920,13 @@
         <v>1.44</v>
       </c>
       <c r="U69" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="V69" t="n">
         <v>1.47</v>
       </c>
       <c r="W69" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X69" t="n">
         <v>42</v>
@@ -17983,7 +17983,7 @@
         <v>17.5</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ69" t="n">
         <v>16</v>
@@ -17992,7 +17992,7 @@
         <v>20</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="AT69" t="n">
         <v>13.5</v>
@@ -18019,7 +18019,7 @@
         <v>20</v>
       </c>
       <c r="BB69" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BC69" t="n">
         <v>14.5</v>
@@ -18028,7 +18028,7 @@
         <v>17.5</v>
       </c>
       <c r="BE69" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BF69" t="n">
         <v>6.8</v>
@@ -18040,13 +18040,13 @@
         <v>5.2</v>
       </c>
       <c r="BI69" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ69" t="n">
         <v>8.4</v>
       </c>
       <c r="BK69" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL69" t="n">
         <v>1000</v>
@@ -18058,7 +18058,7 @@
         <v>6.2</v>
       </c>
       <c r="BO69" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP69" t="n">
         <v>14.5</v>
@@ -18076,7 +18076,7 @@
         <v>7.2</v>
       </c>
       <c r="BU69" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV69" t="n">
         <v>20</v>
@@ -18094,11 +18094,11 @@
         <v>12.5</v>
       </c>
       <c r="CA69" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G70" t="n">
         <v>2.2</v>
@@ -18141,7 +18141,7 @@
         <v>1000</v>
       </c>
       <c r="J70" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="K70" t="n">
         <v>1000</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
         <v>3.8</v>
       </c>
       <c r="K71" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L71" t="n">
         <v>1.42</v>
@@ -18419,7 +18419,7 @@
         <v>1.97</v>
       </c>
       <c r="R71" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S71" t="n">
         <v>3.55</v>
@@ -18446,7 +18446,7 @@
         <v>13</v>
       </c>
       <c r="AA71" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AB71" t="n">
         <v>18</v>
@@ -18455,7 +18455,7 @@
         <v>9</v>
       </c>
       <c r="AD71" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE71" t="n">
         <v>65</v>
@@ -18467,7 +18467,7 @@
         <v>25</v>
       </c>
       <c r="AH71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI71" t="n">
         <v>44</v>
@@ -18488,7 +18488,7 @@
         <v>700</v>
       </c>
       <c r="AO71" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP71" t="n">
         <v>11.5</v>
@@ -18524,22 +18524,22 @@
         <v>15</v>
       </c>
       <c r="BA71" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB71" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC71" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD71" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE71" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF71" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG71" t="n">
         <v>10.5</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -18673,7 +18673,7 @@
         <v>2.32</v>
       </c>
       <c r="R72" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S72" t="n">
         <v>4.4</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -19190,7 +19190,7 @@
         <v>2.18</v>
       </c>
       <c r="U74" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="V74" t="n">
         <v>1.48</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         <v>1000</v>
       </c>
       <c r="J75" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K75" t="n">
         <v>1000</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -19671,7 +19671,7 @@
         <v>3.9</v>
       </c>
       <c r="L76" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M76" t="n">
         <v>1.09</v>
@@ -19818,7 +19818,7 @@
         <v>3.2</v>
       </c>
       <c r="BI76" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="BJ76" t="n">
         <v>12</v>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -19925,7 +19925,7 @@
         <v>4.7</v>
       </c>
       <c r="L77" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M77" t="n">
         <v>1.05</v>
@@ -19952,7 +19952,7 @@
         <v>1.85</v>
       </c>
       <c r="U77" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V77" t="n">
         <v>2.46</v>
@@ -20069,58 +20069,58 @@
         <v>6.6</v>
       </c>
       <c r="BH77" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI77" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ77" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK77" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL77" t="n">
         <v>1000</v>
       </c>
       <c r="BM77" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN77" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO77" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP77" t="n">
         <v>1000</v>
       </c>
       <c r="BQ77" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR77" t="n">
         <v>1000</v>
       </c>
       <c r="BS77" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT77" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU77" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV77" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW77" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BX77" t="n">
         <v>1000</v>
       </c>
       <c r="BY77" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ77" t="n">
         <v>0</v>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -20161,7 +20161,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G78" t="n">
         <v>2.1</v>
@@ -20200,7 +20200,7 @@
         <v>1.28</v>
       </c>
       <c r="S78" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="T78" t="n">
         <v>1.86</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -20448,7 +20448,7 @@
         <v>1.52</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R79" t="n">
         <v>1.19</v>
@@ -20493,7 +20493,7 @@
         <v>500</v>
       </c>
       <c r="AF79" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG79" t="n">
         <v>970</v>
@@ -20529,10 +20529,10 @@
         <v>7</v>
       </c>
       <c r="AR79" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS79" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT79" t="n">
         <v>7</v>
@@ -20541,40 +20541,40 @@
         <v>5.5</v>
       </c>
       <c r="AV79" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW79" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX79" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY79" t="n">
         <v>10</v>
       </c>
       <c r="AZ79" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE79" t="n">
         <v>4.9</v>
       </c>
-      <c r="BA79" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB79" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD79" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE79" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF79" t="n">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="BG79" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH79" t="n">
         <v>2.82</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -20711,7 +20711,7 @@
         <v>4.7</v>
       </c>
       <c r="T80" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U80" t="n">
         <v>1.83</v>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,768 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chilean Segunda Division</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Concon National FC</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Deportes Colina</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-27 20:01:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Itabaiana</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ferroviaria</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="S3" t="n">
-        <v>32</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>380</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>360</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>70</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>320</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>360</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>280</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-27 20:01:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Uruguayan Segunda Division</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Paysandu FC</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Miramar Misiones</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>410</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>250</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>95</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
